--- a/research/traditional_assets/database/data/chile/chile_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_packaging_container.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07948601381846537</v>
+        <v>0.07930425158115553</v>
       </c>
       <c r="C2">
-        <v>412.1839992322784</v>
+        <v>409.1377936602823</v>
       </c>
       <c r="D2">
-        <v>405.3039992322784</v>
+        <v>407.5027936602823</v>
       </c>
       <c r="E2">
-        <v>-349.7</v>
+        <v>-344.455</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.245</v>
       </c>
       <c r="G2">
         <v>6.88</v>
@@ -1576,28 +1576,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2638235</v>
       </c>
       <c r="N2">
-        <v>55.13333333333333</v>
+        <v>54.86950983333333</v>
       </c>
       <c r="O2">
-        <v>14.886</v>
+        <v>14.814767655</v>
       </c>
       <c r="P2">
-        <v>40.24733333333333</v>
+        <v>40.05474217833333</v>
       </c>
       <c r="Q2">
-        <v>81.44733333333332</v>
+        <v>81.25474217833332</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07948601381846537</v>
+        <v>0.07973440563753084</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6215205565223935</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>208.9780983624784</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07930425158115553</v>
+        <v>0.07912248934384568</v>
       </c>
       <c r="C3">
-        <v>409.1377936602823</v>
+        <v>406.1155753594949</v>
       </c>
       <c r="D3">
-        <v>407.5027936602823</v>
+        <v>409.7255753594949</v>
       </c>
       <c r="E3">
-        <v>-344.455</v>
+        <v>-339.21</v>
       </c>
       <c r="F3">
-        <v>5.245</v>
+        <v>10.49</v>
       </c>
       <c r="G3">
         <v>6.88</v>
@@ -1658,28 +1658,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M3">
-        <v>0.2638235</v>
+        <v>0.527647</v>
       </c>
       <c r="N3">
-        <v>54.86950983333333</v>
+        <v>54.60568633333333</v>
       </c>
       <c r="O3">
-        <v>14.814767655</v>
+        <v>14.74353531</v>
       </c>
       <c r="P3">
-        <v>40.05474217833333</v>
+        <v>39.86215102333333</v>
       </c>
       <c r="Q3">
-        <v>81.25474217833332</v>
+        <v>81.06215102333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07973440563753084</v>
+        <v>0.07998786667739355</v>
       </c>
       <c r="T3">
-        <v>0.6215205565223935</v>
+        <v>0.6261627844793195</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>208.9780983624784</v>
+        <v>104.4890491812392</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07912248934384568</v>
+        <v>0.0789407271065358</v>
       </c>
       <c r="C4">
-        <v>406.1155753594949</v>
+        <v>403.1177390086514</v>
       </c>
       <c r="D4">
-        <v>409.7255753594949</v>
+        <v>411.9727390086514</v>
       </c>
       <c r="E4">
-        <v>-339.21</v>
+        <v>-333.965</v>
       </c>
       <c r="F4">
-        <v>10.49</v>
+        <v>15.735</v>
       </c>
       <c r="G4">
         <v>6.88</v>
@@ -1740,28 +1740,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M4">
-        <v>0.527647</v>
+        <v>0.7914705</v>
       </c>
       <c r="N4">
-        <v>54.60568633333333</v>
+        <v>54.34186283333333</v>
       </c>
       <c r="O4">
-        <v>14.74353531</v>
+        <v>14.672302965</v>
       </c>
       <c r="P4">
-        <v>39.86215102333333</v>
+        <v>39.66955986833333</v>
       </c>
       <c r="Q4">
-        <v>81.06215102333333</v>
+        <v>80.86955986833333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07998786667739355</v>
+        <v>0.08024655371807815</v>
       </c>
       <c r="T4">
-        <v>0.6261627844793195</v>
+        <v>0.6309007284765944</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.4890491812392</v>
+        <v>69.65936612082615</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0789407271065358</v>
+        <v>0.07875896486922596</v>
       </c>
       <c r="C5">
-        <v>403.1177390086514</v>
+        <v>400.1446879927893</v>
       </c>
       <c r="D5">
-        <v>411.9727390086514</v>
+        <v>414.2446879927894</v>
       </c>
       <c r="E5">
-        <v>-333.965</v>
+        <v>-328.72</v>
       </c>
       <c r="F5">
-        <v>15.735</v>
+        <v>20.98</v>
       </c>
       <c r="G5">
         <v>6.88</v>
@@ -1822,28 +1822,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M5">
-        <v>0.7914705</v>
+        <v>1.055294</v>
       </c>
       <c r="N5">
-        <v>54.34186283333333</v>
+        <v>54.07803933333334</v>
       </c>
       <c r="O5">
-        <v>14.672302965</v>
+        <v>14.60107062</v>
       </c>
       <c r="P5">
-        <v>39.66955986833333</v>
+        <v>39.47696871333333</v>
       </c>
       <c r="Q5">
-        <v>80.86955986833333</v>
+        <v>80.67696871333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08024655371807815</v>
+        <v>0.08051063007211037</v>
       </c>
       <c r="T5">
-        <v>0.6309007284765944</v>
+        <v>0.6357373796404794</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.65936612082615</v>
+        <v>52.24452459061962</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07875896486922596</v>
+        <v>0.0785772026319161</v>
       </c>
       <c r="C6">
-        <v>400.1446879927893</v>
+        <v>397.1968346446508</v>
       </c>
       <c r="D6">
-        <v>414.2446879927894</v>
+        <v>416.5418346446508</v>
       </c>
       <c r="E6">
-        <v>-328.72</v>
+        <v>-323.475</v>
       </c>
       <c r="F6">
-        <v>20.98</v>
+        <v>26.225</v>
       </c>
       <c r="G6">
         <v>6.88</v>
@@ -1904,28 +1904,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M6">
-        <v>1.055294</v>
+        <v>1.3191175</v>
       </c>
       <c r="N6">
-        <v>54.07803933333334</v>
+        <v>53.81421583333334</v>
       </c>
       <c r="O6">
-        <v>14.60107062</v>
+        <v>14.529838275</v>
       </c>
       <c r="P6">
-        <v>39.47696871333333</v>
+        <v>39.28437755833333</v>
       </c>
       <c r="Q6">
-        <v>80.67696871333334</v>
+        <v>80.48437755833334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08051063007211037</v>
+        <v>0.08078026592833273</v>
       </c>
       <c r="T6">
-        <v>0.6357373796404794</v>
+        <v>0.6406758550393934</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.24452459061962</v>
+        <v>41.7956196724957</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0785772026319161</v>
+        <v>0.07839544039460625</v>
       </c>
       <c r="C7">
-        <v>397.1968346446508</v>
+        <v>394.2746004941557</v>
       </c>
       <c r="D7">
-        <v>416.5418346446508</v>
+        <v>418.8646004941557</v>
       </c>
       <c r="E7">
-        <v>-323.475</v>
+        <v>-318.23</v>
       </c>
       <c r="F7">
-        <v>26.225</v>
+        <v>31.47</v>
       </c>
       <c r="G7">
         <v>6.88</v>
@@ -1986,28 +1986,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M7">
-        <v>1.3191175</v>
+        <v>1.582941</v>
       </c>
       <c r="N7">
-        <v>53.81421583333334</v>
+        <v>53.55039233333333</v>
       </c>
       <c r="O7">
-        <v>14.529838275</v>
+        <v>14.45860593</v>
       </c>
       <c r="P7">
-        <v>39.28437755833333</v>
+        <v>39.09178640333333</v>
       </c>
       <c r="Q7">
-        <v>80.48437755833334</v>
+        <v>80.29178640333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08078026592833273</v>
+        <v>0.08105563871766622</v>
       </c>
       <c r="T7">
-        <v>0.6406758550393934</v>
+        <v>0.6457194043829653</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.7956196724957</v>
+        <v>34.82968306041307</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07839544039460625</v>
+        <v>0.07821367815729639</v>
       </c>
       <c r="C8">
-        <v>394.2746004941557</v>
+        <v>391.378416526272</v>
       </c>
       <c r="D8">
-        <v>418.8646004941557</v>
+        <v>421.2134165262719</v>
       </c>
       <c r="E8">
-        <v>-318.23</v>
+        <v>-312.985</v>
       </c>
       <c r="F8">
-        <v>31.47</v>
+        <v>36.715</v>
       </c>
       <c r="G8">
         <v>6.88</v>
@@ -2068,28 +2068,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M8">
-        <v>1.582941</v>
+        <v>1.8467645</v>
       </c>
       <c r="N8">
-        <v>53.55039233333333</v>
+        <v>53.28656883333333</v>
       </c>
       <c r="O8">
-        <v>14.45860593</v>
+        <v>14.387373585</v>
       </c>
       <c r="P8">
-        <v>39.09178640333333</v>
+        <v>38.89919524833333</v>
       </c>
       <c r="Q8">
-        <v>80.29178640333333</v>
+        <v>80.09919524833333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08105563871766622</v>
+        <v>0.08133693350246923</v>
       </c>
       <c r="T8">
-        <v>0.6457194043829653</v>
+        <v>0.6508714171532805</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.82968306041307</v>
+        <v>29.85401405178264</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07821367815729638</v>
+        <v>0.07803191591998654</v>
       </c>
       <c r="C9">
-        <v>391.3784165262722</v>
+        <v>388.5087234476105</v>
       </c>
       <c r="D9">
-        <v>421.2134165262722</v>
+        <v>423.5887234476104</v>
       </c>
       <c r="E9">
-        <v>-312.985</v>
+        <v>-307.74</v>
       </c>
       <c r="F9">
-        <v>36.715</v>
+        <v>41.96</v>
       </c>
       <c r="G9">
         <v>6.88</v>
@@ -2150,28 +2150,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M9">
-        <v>1.8467645</v>
+        <v>2.110588</v>
       </c>
       <c r="N9">
-        <v>53.28656883333333</v>
+        <v>53.02274533333333</v>
       </c>
       <c r="O9">
-        <v>14.387373585</v>
+        <v>14.31614124</v>
       </c>
       <c r="P9">
-        <v>38.89919524833333</v>
+        <v>38.70660409333333</v>
       </c>
       <c r="Q9">
-        <v>80.09919524833333</v>
+        <v>79.90660409333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08133693350246923</v>
+        <v>0.08162434339128971</v>
       </c>
       <c r="T9">
-        <v>0.6508714171532805</v>
+        <v>0.6561354302012113</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.85401405178263</v>
+        <v>26.12226229530981</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07803191591998654</v>
+        <v>0.07785015368267667</v>
       </c>
       <c r="C10">
-        <v>388.5087234476105</v>
+        <v>385.6659719620906</v>
       </c>
       <c r="D10">
-        <v>423.5887234476104</v>
+        <v>425.9909719620906</v>
       </c>
       <c r="E10">
-        <v>-307.74</v>
+        <v>-302.495</v>
       </c>
       <c r="F10">
-        <v>41.96</v>
+        <v>47.205</v>
       </c>
       <c r="G10">
         <v>6.88</v>
@@ -2232,28 +2232,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M10">
-        <v>2.110588</v>
+        <v>2.3744115</v>
       </c>
       <c r="N10">
-        <v>53.02274533333333</v>
+        <v>52.75892183333333</v>
       </c>
       <c r="O10">
-        <v>14.31614124</v>
+        <v>14.244908895</v>
       </c>
       <c r="P10">
-        <v>38.70660409333333</v>
+        <v>38.51401293833333</v>
       </c>
       <c r="Q10">
-        <v>79.90660409333333</v>
+        <v>79.71401293833333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08162434339128971</v>
+        <v>0.08191806998096338</v>
       </c>
       <c r="T10">
-        <v>0.6561354302012113</v>
+        <v>0.6615151358436022</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.12226229530981</v>
+        <v>23.21978870694205</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07785015368267667</v>
+        <v>0.07766839144536683</v>
       </c>
       <c r="C11">
-        <v>385.6659719620906</v>
+        <v>382.8506230560393</v>
       </c>
       <c r="D11">
-        <v>425.9909719620906</v>
+        <v>428.4206230560393</v>
       </c>
       <c r="E11">
-        <v>-302.495</v>
+        <v>-297.25</v>
       </c>
       <c r="F11">
-        <v>47.205</v>
+        <v>52.45</v>
       </c>
       <c r="G11">
         <v>6.88</v>
@@ -2314,28 +2314,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M11">
-        <v>2.3744115</v>
+        <v>2.638234999999999</v>
       </c>
       <c r="N11">
-        <v>52.75892183333333</v>
+        <v>52.49509833333333</v>
       </c>
       <c r="O11">
-        <v>14.244908895</v>
+        <v>14.17367655</v>
       </c>
       <c r="P11">
-        <v>38.51401293833333</v>
+        <v>38.32142178333334</v>
       </c>
       <c r="Q11">
-        <v>79.71401293833333</v>
+        <v>79.52142178333332</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08191806998096338</v>
+        <v>0.08221832382818536</v>
       </c>
       <c r="T11">
-        <v>0.6615151358436022</v>
+        <v>0.6670143905002685</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.21978870694205</v>
+        <v>20.89780983624785</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07766839144536683</v>
+        <v>0.07748662920805695</v>
       </c>
       <c r="C12">
-        <v>382.8506230560393</v>
+        <v>380.0631482931055</v>
       </c>
       <c r="D12">
-        <v>428.4206230560393</v>
+        <v>430.8781482931055</v>
       </c>
       <c r="E12">
-        <v>-297.25</v>
+        <v>-292.005</v>
       </c>
       <c r="F12">
-        <v>52.45</v>
+        <v>57.695</v>
       </c>
       <c r="G12">
         <v>6.88</v>
@@ -2396,28 +2396,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M12">
-        <v>2.638235</v>
+        <v>2.9020585</v>
       </c>
       <c r="N12">
-        <v>52.49509833333333</v>
+        <v>52.23127483333333</v>
       </c>
       <c r="O12">
-        <v>14.17367655</v>
+        <v>14.102444205</v>
       </c>
       <c r="P12">
-        <v>38.32142178333334</v>
+        <v>38.12883062833333</v>
       </c>
       <c r="Q12">
-        <v>79.52142178333332</v>
+        <v>79.32883062833332</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08221832382818536</v>
+        <v>0.08252532495287299</v>
       </c>
       <c r="T12">
-        <v>0.6670143905002685</v>
+        <v>0.6726372239132642</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.89780983624784</v>
+        <v>18.99800894204349</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07748662920805695</v>
+        <v>0.07730486697074711</v>
       </c>
       <c r="C13">
-        <v>380.0631482931055</v>
+        <v>377.3040301193768</v>
       </c>
       <c r="D13">
-        <v>430.8781482931055</v>
+        <v>433.3640301193768</v>
       </c>
       <c r="E13">
-        <v>-292.005</v>
+        <v>-286.76</v>
       </c>
       <c r="F13">
-        <v>57.695</v>
+        <v>62.94</v>
       </c>
       <c r="G13">
         <v>6.88</v>
@@ -2478,28 +2478,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M13">
-        <v>2.9020585</v>
+        <v>3.165882</v>
       </c>
       <c r="N13">
-        <v>52.23127483333333</v>
+        <v>51.96745133333333</v>
       </c>
       <c r="O13">
-        <v>14.102444205</v>
+        <v>14.03121186</v>
       </c>
       <c r="P13">
-        <v>38.12883062833333</v>
+        <v>37.93623947333333</v>
       </c>
       <c r="Q13">
-        <v>79.32883062833332</v>
+        <v>79.13623947333332</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08252532495287299</v>
+        <v>0.08283930337584898</v>
       </c>
       <c r="T13">
-        <v>0.6726372239132642</v>
+        <v>0.6783878489947371</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.99800894204349</v>
+        <v>17.41484153020654</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07730486697074711</v>
+        <v>0.07712310473343725</v>
       </c>
       <c r="C14">
-        <v>377.3040301193768</v>
+        <v>374.5737621791279</v>
       </c>
       <c r="D14">
-        <v>433.3640301193768</v>
+        <v>435.8787621791279</v>
       </c>
       <c r="E14">
-        <v>-286.76</v>
+        <v>-281.515</v>
       </c>
       <c r="F14">
-        <v>62.94</v>
+        <v>68.185</v>
       </c>
       <c r="G14">
         <v>6.88</v>
@@ -2560,28 +2560,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M14">
-        <v>3.165882</v>
+        <v>3.4297055</v>
       </c>
       <c r="N14">
-        <v>51.96745133333333</v>
+        <v>51.70362783333334</v>
       </c>
       <c r="O14">
-        <v>14.03121186</v>
+        <v>13.959979515</v>
       </c>
       <c r="P14">
-        <v>37.93623947333333</v>
+        <v>37.74364831833334</v>
       </c>
       <c r="Q14">
-        <v>79.13623947333332</v>
+        <v>78.94364831833333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08283930337584898</v>
+        <v>0.08316049969360603</v>
       </c>
       <c r="T14">
-        <v>0.6783878489947371</v>
+        <v>0.6842706723539451</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.41484153020654</v>
+        <v>16.07523833557526</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07712310473343725</v>
+        <v>0.0769413424961274</v>
       </c>
       <c r="C15">
-        <v>374.5737621791279</v>
+        <v>371.8728496416186</v>
       </c>
       <c r="D15">
-        <v>435.8787621791279</v>
+        <v>438.4228496416186</v>
       </c>
       <c r="E15">
-        <v>-281.515</v>
+        <v>-276.27</v>
       </c>
       <c r="F15">
-        <v>68.185</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="G15">
         <v>6.88</v>
@@ -2642,28 +2642,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M15">
-        <v>3.4297055</v>
+        <v>3.693529</v>
       </c>
       <c r="N15">
-        <v>51.70362783333334</v>
+        <v>51.43980433333333</v>
       </c>
       <c r="O15">
-        <v>13.959979515</v>
+        <v>13.88874717</v>
       </c>
       <c r="P15">
-        <v>37.74364831833334</v>
+        <v>37.55105716333333</v>
       </c>
       <c r="Q15">
-        <v>78.94364831833333</v>
+        <v>78.75105716333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08316049969360603</v>
+        <v>0.08348916569317139</v>
       </c>
       <c r="T15">
-        <v>0.6842706723539451</v>
+        <v>0.6902903055587161</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.07523833557526</v>
+        <v>14.92700702589132</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0769413424961274</v>
+        <v>0.07675958025881753</v>
       </c>
       <c r="C16">
-        <v>371.8728496416186</v>
+        <v>369.2018095394093</v>
       </c>
       <c r="D16">
-        <v>438.4228496416186</v>
+        <v>440.9968095394093</v>
       </c>
       <c r="E16">
-        <v>-276.27</v>
+        <v>-271.025</v>
       </c>
       <c r="F16">
-        <v>73.43000000000001</v>
+        <v>78.67500000000001</v>
       </c>
       <c r="G16">
         <v>6.88</v>
@@ -2724,28 +2724,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M16">
-        <v>3.693529</v>
+        <v>3.9573525</v>
       </c>
       <c r="N16">
-        <v>51.43980433333333</v>
+        <v>51.17598083333333</v>
       </c>
       <c r="O16">
-        <v>13.88874717</v>
+        <v>13.817514825</v>
       </c>
       <c r="P16">
-        <v>37.55105716333333</v>
+        <v>37.35846600833333</v>
       </c>
       <c r="Q16">
-        <v>78.75105716333333</v>
+        <v>78.55846600833333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08348916569317139</v>
+        <v>0.08382556501037357</v>
       </c>
       <c r="T16">
-        <v>0.6902903055587161</v>
+        <v>0.6964515771918346</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.92700702589132</v>
+        <v>13.93187322416523</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07675958025881753</v>
+        <v>0.07657781802150768</v>
       </c>
       <c r="C17">
-        <v>369.2018095394093</v>
+        <v>366.5611711186602</v>
       </c>
       <c r="D17">
-        <v>440.9968095394093</v>
+        <v>443.6011711186602</v>
       </c>
       <c r="E17">
-        <v>-271.025</v>
+        <v>-265.78</v>
       </c>
       <c r="F17">
-        <v>78.675</v>
+        <v>83.92</v>
       </c>
       <c r="G17">
         <v>6.88</v>
@@ -2806,28 +2806,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M17">
-        <v>3.9573525</v>
+        <v>4.221176</v>
       </c>
       <c r="N17">
-        <v>51.17598083333333</v>
+        <v>50.91215733333333</v>
       </c>
       <c r="O17">
-        <v>13.817514825</v>
+        <v>13.74628248</v>
       </c>
       <c r="P17">
-        <v>37.35846600833333</v>
+        <v>37.16587485333334</v>
       </c>
       <c r="Q17">
-        <v>78.55846600833333</v>
+        <v>78.36587485333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08382556501037357</v>
+        <v>0.0841699738351282</v>
       </c>
       <c r="T17">
-        <v>0.6964515771918346</v>
+        <v>0.7027595457685988</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.93187322416523</v>
+        <v>13.0611311476549</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07657781802150768</v>
+        <v>0.07658220578419782</v>
       </c>
       <c r="C18">
-        <v>366.5611711186602</v>
+        <v>361.2529392410753</v>
       </c>
       <c r="D18">
-        <v>443.6011711186602</v>
+        <v>443.5379392410753</v>
       </c>
       <c r="E18">
-        <v>-265.78</v>
+        <v>-260.535</v>
       </c>
       <c r="F18">
-        <v>83.92</v>
+        <v>89.16500000000001</v>
       </c>
       <c r="G18">
         <v>6.88</v>
@@ -2888,45 +2888,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M18">
-        <v>4.221176</v>
+        <v>4.618747</v>
       </c>
       <c r="N18">
-        <v>50.91215733333333</v>
+        <v>50.51458633333333</v>
       </c>
       <c r="O18">
-        <v>13.74628248</v>
+        <v>13.63893831</v>
       </c>
       <c r="P18">
-        <v>37.16587485333334</v>
+        <v>36.87564802333333</v>
       </c>
       <c r="Q18">
-        <v>78.36587485333334</v>
+        <v>78.07564802333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0841699738351282</v>
+        <v>0.08452268166770822</v>
       </c>
       <c r="T18">
-        <v>0.7027595457685988</v>
+        <v>0.7092195135881766</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.0611311476549</v>
+        <v>11.9368593545681</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07658220578419782</v>
+        <v>0.07641139354688795</v>
       </c>
       <c r="C19">
-        <v>361.2529392410753</v>
+        <v>358.4828905240848</v>
       </c>
       <c r="D19">
-        <v>443.5379392410753</v>
+        <v>446.0128905240848</v>
       </c>
       <c r="E19">
-        <v>-260.535</v>
+        <v>-255.29</v>
       </c>
       <c r="F19">
-        <v>89.16500000000001</v>
+        <v>94.41000000000001</v>
       </c>
       <c r="G19">
         <v>6.88</v>
@@ -2970,28 +2970,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M19">
-        <v>4.618747</v>
+        <v>4.890438000000001</v>
       </c>
       <c r="N19">
-        <v>50.51458633333333</v>
+        <v>50.24289533333333</v>
       </c>
       <c r="O19">
-        <v>13.63893831</v>
+        <v>13.56558174</v>
       </c>
       <c r="P19">
-        <v>36.87564802333333</v>
+        <v>36.67731359333333</v>
       </c>
       <c r="Q19">
-        <v>78.07564802333333</v>
+        <v>77.87731359333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08452268166770822</v>
+        <v>0.08488399213035117</v>
       </c>
       <c r="T19">
-        <v>0.7092195135881766</v>
+        <v>0.7158370415984756</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.9368593545681</v>
+        <v>11.27370050153653</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07641139354688796</v>
+        <v>0.0762405813095781</v>
       </c>
       <c r="C20">
-        <v>358.4828905240846</v>
+        <v>355.7406173585254</v>
       </c>
       <c r="D20">
-        <v>446.0128905240846</v>
+        <v>448.5156173585254</v>
       </c>
       <c r="E20">
-        <v>-255.29</v>
+        <v>-250.045</v>
       </c>
       <c r="F20">
-        <v>94.41</v>
+        <v>99.655</v>
       </c>
       <c r="G20">
         <v>6.88</v>
@@ -3052,28 +3052,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M20">
-        <v>4.890438</v>
+        <v>5.162129</v>
       </c>
       <c r="N20">
-        <v>50.24289533333334</v>
+        <v>49.97120433333333</v>
       </c>
       <c r="O20">
-        <v>13.56558174</v>
+        <v>13.49222517</v>
       </c>
       <c r="P20">
-        <v>36.67731359333334</v>
+        <v>36.47897916333334</v>
       </c>
       <c r="Q20">
-        <v>77.87731359333333</v>
+        <v>77.67897916333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08488399213035117</v>
+        <v>0.08525422383898532</v>
       </c>
       <c r="T20">
-        <v>0.7158370415984756</v>
+        <v>0.7226179653621156</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.27370050153654</v>
+        <v>10.68034784356093</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0762405813095781</v>
+        <v>0.07606976907226826</v>
       </c>
       <c r="C21">
-        <v>355.7406173585254</v>
+        <v>353.026589956516</v>
       </c>
       <c r="D21">
-        <v>448.5156173585254</v>
+        <v>451.046589956516</v>
       </c>
       <c r="E21">
-        <v>-250.045</v>
+        <v>-244.8</v>
       </c>
       <c r="F21">
-        <v>99.655</v>
+        <v>104.9</v>
       </c>
       <c r="G21">
         <v>6.88</v>
@@ -3134,28 +3134,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M21">
-        <v>5.162129</v>
+        <v>5.43382</v>
       </c>
       <c r="N21">
-        <v>49.97120433333333</v>
+        <v>49.69951333333334</v>
       </c>
       <c r="O21">
-        <v>13.49222517</v>
+        <v>13.4188686</v>
       </c>
       <c r="P21">
-        <v>36.47897916333334</v>
+        <v>36.28064473333333</v>
       </c>
       <c r="Q21">
-        <v>77.67897916333334</v>
+        <v>77.48064473333332</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08525422383898532</v>
+        <v>0.08563371134033532</v>
       </c>
       <c r="T21">
-        <v>0.7226179653621156</v>
+        <v>0.7295684122198466</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.68034784356093</v>
+        <v>10.14633045138288</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07606976907226826</v>
+        <v>0.07615956683495839</v>
       </c>
       <c r="C22">
-        <v>353.026589956516</v>
+        <v>346.4474808479343</v>
       </c>
       <c r="D22">
-        <v>451.046589956516</v>
+        <v>449.7124808479344</v>
       </c>
       <c r="E22">
-        <v>-244.8</v>
+        <v>-239.555</v>
       </c>
       <c r="F22">
-        <v>104.9</v>
+        <v>110.145</v>
       </c>
       <c r="G22">
         <v>6.88</v>
@@ -3216,45 +3216,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M22">
-        <v>5.43382</v>
+        <v>5.8927575</v>
       </c>
       <c r="N22">
-        <v>49.69951333333334</v>
+        <v>49.24057583333333</v>
       </c>
       <c r="O22">
-        <v>13.4188686</v>
+        <v>13.294955475</v>
       </c>
       <c r="P22">
-        <v>36.28064473333333</v>
+        <v>35.94562035833333</v>
       </c>
       <c r="Q22">
-        <v>77.48064473333332</v>
+        <v>77.14562035833333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08563371134033532</v>
+        <v>0.0860228061202005</v>
       </c>
       <c r="T22">
-        <v>0.7295684122198466</v>
+        <v>0.7366948197575199</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.14633045138288</v>
+        <v>9.356117799406022</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07615956683495839</v>
+        <v>0.07600116459764854</v>
       </c>
       <c r="C23">
-        <v>346.4474808479344</v>
+        <v>343.5611800590908</v>
       </c>
       <c r="D23">
-        <v>449.7124808479344</v>
+        <v>452.0711800590908</v>
       </c>
       <c r="E23">
-        <v>-239.555</v>
+        <v>-234.31</v>
       </c>
       <c r="F23">
-        <v>110.145</v>
+        <v>115.39</v>
       </c>
       <c r="G23">
         <v>6.88</v>
@@ -3298,28 +3298,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M23">
-        <v>5.8927575</v>
+        <v>6.173365</v>
       </c>
       <c r="N23">
-        <v>49.24057583333333</v>
+        <v>48.95996833333334</v>
       </c>
       <c r="O23">
-        <v>13.294955475</v>
+        <v>13.21919145</v>
       </c>
       <c r="P23">
-        <v>35.94562035833333</v>
+        <v>35.74077688333333</v>
       </c>
       <c r="Q23">
-        <v>77.14562035833333</v>
+        <v>76.94077688333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0860228061202005</v>
+        <v>0.08642187768929299</v>
       </c>
       <c r="T23">
-        <v>0.7366948197575199</v>
+        <v>0.7440039556935953</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.356117799406022</v>
+        <v>8.930839717614841</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07600116459764854</v>
+        <v>0.07584276236033868</v>
       </c>
       <c r="C24">
-        <v>343.5611800590908</v>
+        <v>340.6997520317933</v>
       </c>
       <c r="D24">
-        <v>452.0711800590908</v>
+        <v>454.4547520317933</v>
       </c>
       <c r="E24">
-        <v>-234.31</v>
+        <v>-229.065</v>
       </c>
       <c r="F24">
-        <v>115.39</v>
+        <v>120.635</v>
       </c>
       <c r="G24">
         <v>6.88</v>
@@ -3380,28 +3380,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M24">
-        <v>6.173365</v>
+        <v>6.4539725</v>
       </c>
       <c r="N24">
-        <v>48.95996833333334</v>
+        <v>48.67936083333333</v>
       </c>
       <c r="O24">
-        <v>13.21919145</v>
+        <v>13.143427425</v>
       </c>
       <c r="P24">
-        <v>35.74077688333333</v>
+        <v>35.53593340833334</v>
       </c>
       <c r="Q24">
-        <v>76.94077688333333</v>
+        <v>76.73593340833332</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08642187768929299</v>
+        <v>0.08683131475368661</v>
       </c>
       <c r="T24">
-        <v>0.7440039556935953</v>
+        <v>0.7515029393163219</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.930839717614841</v>
+        <v>8.542542338588108</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07584276236033868</v>
+        <v>0.07568436012302883</v>
       </c>
       <c r="C25">
-        <v>340.6997520317933</v>
+        <v>337.8635922807254</v>
       </c>
       <c r="D25">
-        <v>454.4547520317933</v>
+        <v>456.8635922807254</v>
       </c>
       <c r="E25">
-        <v>-229.065</v>
+        <v>-223.82</v>
       </c>
       <c r="F25">
-        <v>120.635</v>
+        <v>125.88</v>
       </c>
       <c r="G25">
         <v>6.88</v>
@@ -3462,28 +3462,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M25">
-        <v>6.4539725</v>
+        <v>6.73458</v>
       </c>
       <c r="N25">
-        <v>48.67936083333333</v>
+        <v>48.39875333333333</v>
       </c>
       <c r="O25">
-        <v>13.143427425</v>
+        <v>13.0676634</v>
       </c>
       <c r="P25">
-        <v>35.53593340833334</v>
+        <v>35.33108993333333</v>
       </c>
       <c r="Q25">
-        <v>76.73593340833332</v>
+        <v>76.53108993333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08683131475368661</v>
+        <v>0.08725152647766951</v>
       </c>
       <c r="T25">
-        <v>0.7515029393163219</v>
+        <v>0.7591992646133309</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.542542338588108</v>
+        <v>8.186603074480269</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07568436012302883</v>
+        <v>0.07552595788571896</v>
       </c>
       <c r="C26">
-        <v>337.8635922807254</v>
+        <v>335.053104750968</v>
       </c>
       <c r="D26">
-        <v>456.8635922807254</v>
+        <v>459.298104750968</v>
       </c>
       <c r="E26">
-        <v>-223.82</v>
+        <v>-218.575</v>
       </c>
       <c r="F26">
-        <v>125.88</v>
+        <v>131.125</v>
       </c>
       <c r="G26">
         <v>6.88</v>
@@ -3544,28 +3544,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M26">
-        <v>6.734579999999999</v>
+        <v>7.0151875</v>
       </c>
       <c r="N26">
-        <v>48.39875333333333</v>
+        <v>48.11814583333333</v>
       </c>
       <c r="O26">
-        <v>13.0676634</v>
+        <v>12.991899375</v>
       </c>
       <c r="P26">
-        <v>35.33108993333333</v>
+        <v>35.12624645833333</v>
       </c>
       <c r="Q26">
-        <v>76.53108993333333</v>
+        <v>76.32624645833332</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08725152647766951</v>
+        <v>0.08768294384762529</v>
       </c>
       <c r="T26">
-        <v>0.7591992646133309</v>
+        <v>0.7671008252515934</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.186603074480271</v>
+        <v>7.859138951501058</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07552595788571896</v>
+        <v>0.07551939564840912</v>
       </c>
       <c r="C27">
-        <v>335.053104750968</v>
+        <v>329.9095207822693</v>
       </c>
       <c r="D27">
-        <v>459.298104750968</v>
+        <v>459.3995207822693</v>
       </c>
       <c r="E27">
-        <v>-218.575</v>
+        <v>-213.33</v>
       </c>
       <c r="F27">
-        <v>131.125</v>
+        <v>136.37</v>
       </c>
       <c r="G27">
         <v>6.88</v>
@@ -3626,45 +3626,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M27">
-        <v>7.0151875</v>
+        <v>7.404891</v>
       </c>
       <c r="N27">
-        <v>48.11814583333333</v>
+        <v>47.72844233333333</v>
       </c>
       <c r="O27">
-        <v>12.991899375</v>
+        <v>12.88667943</v>
       </c>
       <c r="P27">
-        <v>35.12624645833333</v>
+        <v>34.84176290333333</v>
       </c>
       <c r="Q27">
-        <v>76.32624645833332</v>
+        <v>76.04176290333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08768294384762529</v>
+        <v>0.0881260211464988</v>
       </c>
       <c r="T27">
-        <v>0.7671008252515934</v>
+        <v>0.7752159415827818</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.859138951501058</v>
+        <v>7.445529358005855</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07551939564840912</v>
+        <v>0.07536683341109926</v>
       </c>
       <c r="C28">
-        <v>329.9095207822693</v>
+        <v>327.0349815527931</v>
       </c>
       <c r="D28">
-        <v>459.3995207822693</v>
+        <v>461.7699815527931</v>
       </c>
       <c r="E28">
-        <v>-213.33</v>
+        <v>-208.085</v>
       </c>
       <c r="F28">
-        <v>136.37</v>
+        <v>141.615</v>
       </c>
       <c r="G28">
         <v>6.88</v>
@@ -3708,28 +3708,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M28">
-        <v>7.404891</v>
+        <v>7.689694500000001</v>
       </c>
       <c r="N28">
-        <v>47.72844233333333</v>
+        <v>47.44363883333333</v>
       </c>
       <c r="O28">
-        <v>12.88667943</v>
+        <v>12.809782485</v>
       </c>
       <c r="P28">
-        <v>34.84176290333333</v>
+        <v>34.63385634833333</v>
       </c>
       <c r="Q28">
-        <v>76.04176290333334</v>
+        <v>75.83385634833333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0881260211464988</v>
+        <v>0.08858123754945103</v>
       </c>
       <c r="T28">
-        <v>0.7752159415827818</v>
+        <v>0.7835533898682495</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.445529358005855</v>
+        <v>7.169769011413044</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07536683341109926</v>
+        <v>0.07521427117378938</v>
       </c>
       <c r="C29">
-        <v>327.0349815527931</v>
+        <v>324.1850319380974</v>
       </c>
       <c r="D29">
-        <v>461.7699815527931</v>
+        <v>464.1650319380975</v>
       </c>
       <c r="E29">
-        <v>-208.085</v>
+        <v>-202.84</v>
       </c>
       <c r="F29">
-        <v>141.615</v>
+        <v>146.86</v>
       </c>
       <c r="G29">
         <v>6.88</v>
@@ -3790,28 +3790,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M29">
-        <v>7.689694500000001</v>
+        <v>7.974498000000001</v>
       </c>
       <c r="N29">
-        <v>47.44363883333333</v>
+        <v>47.15883533333333</v>
       </c>
       <c r="O29">
-        <v>12.809782485</v>
+        <v>12.73288554</v>
       </c>
       <c r="P29">
-        <v>34.63385634833333</v>
+        <v>34.42594979333333</v>
       </c>
       <c r="Q29">
-        <v>75.83385634833333</v>
+        <v>75.62594979333332</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08858123754945103</v>
+        <v>0.08904909885248527</v>
       </c>
       <c r="T29">
-        <v>0.7835533898682495</v>
+        <v>0.7921224339394246</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.169769011413044</v>
+        <v>6.913705832434007</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07521427117378938</v>
+        <v>0.07506170893647954</v>
       </c>
       <c r="C30">
-        <v>324.1850319380974</v>
+        <v>321.3600565479791</v>
       </c>
       <c r="D30">
-        <v>464.1650319380975</v>
+        <v>466.5850565479791</v>
       </c>
       <c r="E30">
-        <v>-202.84</v>
+        <v>-197.595</v>
       </c>
       <c r="F30">
-        <v>146.86</v>
+        <v>152.105</v>
       </c>
       <c r="G30">
         <v>6.88</v>
@@ -3872,28 +3872,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M30">
-        <v>7.974498000000001</v>
+        <v>8.259301500000001</v>
       </c>
       <c r="N30">
-        <v>47.15883533333333</v>
+        <v>46.87403183333333</v>
       </c>
       <c r="O30">
-        <v>12.73288554</v>
+        <v>12.655988595</v>
       </c>
       <c r="P30">
-        <v>34.42594979333333</v>
+        <v>34.21804323833334</v>
       </c>
       <c r="Q30">
-        <v>75.62594979333332</v>
+        <v>75.41804323833333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08904909885248527</v>
+        <v>0.08953013934715429</v>
       </c>
       <c r="T30">
-        <v>0.7921224339394246</v>
+        <v>0.8009328595337314</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.913705832434007</v>
+        <v>6.675302183039731</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07506170893647954</v>
+        <v>0.07490914669916969</v>
       </c>
       <c r="C31">
-        <v>321.3600565479791</v>
+        <v>318.5604480552586</v>
       </c>
       <c r="D31">
-        <v>466.5850565479791</v>
+        <v>469.0304480552585</v>
       </c>
       <c r="E31">
-        <v>-197.595</v>
+        <v>-192.35</v>
       </c>
       <c r="F31">
-        <v>152.105</v>
+        <v>157.35</v>
       </c>
       <c r="G31">
         <v>6.88</v>
@@ -3954,28 +3954,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M31">
-        <v>8.259301499999999</v>
+        <v>8.544105</v>
       </c>
       <c r="N31">
-        <v>46.87403183333333</v>
+        <v>46.58922833333333</v>
       </c>
       <c r="O31">
-        <v>12.655988595</v>
+        <v>12.57909165</v>
       </c>
       <c r="P31">
-        <v>34.21804323833334</v>
+        <v>34.01013668333333</v>
       </c>
       <c r="Q31">
-        <v>75.41804323833333</v>
+        <v>75.21013668333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08953013934715429</v>
+        <v>0.0900249238559567</v>
       </c>
       <c r="T31">
-        <v>0.8009328595337314</v>
+        <v>0.8099950115735898</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.675302183039732</v>
+        <v>6.452792110271741</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07490914669916969</v>
+        <v>0.07475658446185982</v>
       </c>
       <c r="C32">
-        <v>318.5604480552586</v>
+        <v>315.7866074081862</v>
       </c>
       <c r="D32">
-        <v>469.0304480552585</v>
+        <v>471.5016074081862</v>
       </c>
       <c r="E32">
-        <v>-192.35</v>
+        <v>-187.105</v>
       </c>
       <c r="F32">
-        <v>157.35</v>
+        <v>162.595</v>
       </c>
       <c r="G32">
         <v>6.88</v>
@@ -4036,28 +4036,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M32">
-        <v>8.544105</v>
+        <v>8.828908500000001</v>
       </c>
       <c r="N32">
-        <v>46.58922833333333</v>
+        <v>46.30442483333333</v>
       </c>
       <c r="O32">
-        <v>12.57909165</v>
+        <v>12.502194705</v>
       </c>
       <c r="P32">
-        <v>34.01013668333333</v>
+        <v>33.80223012833333</v>
       </c>
       <c r="Q32">
-        <v>75.21013668333333</v>
+        <v>75.00223012833332</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0900249238559567</v>
+        <v>0.09053404994472439</v>
       </c>
       <c r="T32">
-        <v>0.8099950115735898</v>
+        <v>0.8193198346870673</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.452792110271741</v>
+        <v>6.244637526069425</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07475658446185982</v>
+        <v>0.07483762222454997</v>
       </c>
       <c r="C33">
-        <v>315.7866074081862</v>
+        <v>309.2257477598412</v>
       </c>
       <c r="D33">
-        <v>471.5016074081862</v>
+        <v>470.1857477598412</v>
       </c>
       <c r="E33">
-        <v>-187.105</v>
+        <v>-181.86</v>
       </c>
       <c r="F33">
-        <v>162.595</v>
+        <v>167.84</v>
       </c>
       <c r="G33">
         <v>6.88</v>
@@ -4118,45 +4118,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M33">
-        <v>8.828908500000001</v>
+        <v>9.281552000000001</v>
       </c>
       <c r="N33">
-        <v>46.30442483333333</v>
+        <v>45.85178133333334</v>
       </c>
       <c r="O33">
-        <v>12.502194705</v>
+        <v>12.37998096</v>
       </c>
       <c r="P33">
-        <v>33.80223012833333</v>
+        <v>33.47180037333334</v>
       </c>
       <c r="Q33">
-        <v>75.00223012833332</v>
+        <v>74.67180037333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09053404994472439</v>
+        <v>0.09105815033022055</v>
       </c>
       <c r="T33">
-        <v>0.8193198346870673</v>
+        <v>0.8289189173038823</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.244637526069425</v>
+        <v>5.940098523752636</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07483762222454997</v>
+        <v>0.07469235998724011</v>
       </c>
       <c r="C34">
-        <v>309.2257477598412</v>
+        <v>306.344702580457</v>
       </c>
       <c r="D34">
-        <v>470.1857477598412</v>
+        <v>472.549702580457</v>
       </c>
       <c r="E34">
-        <v>-181.86</v>
+        <v>-176.615</v>
       </c>
       <c r="F34">
-        <v>167.84</v>
+        <v>173.085</v>
       </c>
       <c r="G34">
         <v>6.88</v>
@@ -4200,28 +4200,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M34">
-        <v>9.281552000000001</v>
+        <v>9.571600500000001</v>
       </c>
       <c r="N34">
-        <v>45.85178133333334</v>
+        <v>45.56173283333333</v>
       </c>
       <c r="O34">
-        <v>12.37998096</v>
+        <v>12.301667865</v>
       </c>
       <c r="P34">
-        <v>33.47180037333334</v>
+        <v>33.26006496833333</v>
       </c>
       <c r="Q34">
-        <v>74.67180037333333</v>
+        <v>74.46006496833333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09105815033022055</v>
+        <v>0.09159789550334346</v>
       </c>
       <c r="T34">
-        <v>0.8289189173038823</v>
+        <v>0.8388045397003038</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.940098523752636</v>
+        <v>5.760095538184374</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07469235998724011</v>
+        <v>0.07454709774993025</v>
       </c>
       <c r="C35">
-        <v>306.344702580457</v>
+        <v>303.4875480469481</v>
       </c>
       <c r="D35">
-        <v>472.549702580457</v>
+        <v>474.9375480469481</v>
       </c>
       <c r="E35">
-        <v>-176.615</v>
+        <v>-171.37</v>
       </c>
       <c r="F35">
-        <v>173.085</v>
+        <v>178.33</v>
       </c>
       <c r="G35">
         <v>6.88</v>
@@ -4282,28 +4282,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M35">
-        <v>9.571600500000001</v>
+        <v>9.861649000000002</v>
       </c>
       <c r="N35">
-        <v>45.56173283333333</v>
+        <v>45.27168433333333</v>
       </c>
       <c r="O35">
-        <v>12.301667865</v>
+        <v>12.22335477</v>
       </c>
       <c r="P35">
-        <v>33.26006496833333</v>
+        <v>33.04832956333333</v>
       </c>
       <c r="Q35">
-        <v>74.46006496833333</v>
+        <v>74.24832956333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09159789550334346</v>
+        <v>0.09215399659080342</v>
       </c>
       <c r="T35">
-        <v>0.8388045397003038</v>
+        <v>0.8489897264117683</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.760095538184374</v>
+        <v>5.590680963531892</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07454709774993025</v>
+        <v>0.0744018355126204</v>
       </c>
       <c r="C36">
-        <v>303.4875480469481</v>
+        <v>300.6546481648342</v>
       </c>
       <c r="D36">
-        <v>474.9375480469481</v>
+        <v>477.3496481648342</v>
       </c>
       <c r="E36">
-        <v>-171.37</v>
+        <v>-166.125</v>
       </c>
       <c r="F36">
-        <v>178.33</v>
+        <v>183.575</v>
       </c>
       <c r="G36">
         <v>6.88</v>
@@ -4364,28 +4364,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M36">
-        <v>9.861649000000002</v>
+        <v>10.1516975</v>
       </c>
       <c r="N36">
-        <v>45.27168433333333</v>
+        <v>44.98163583333333</v>
       </c>
       <c r="O36">
-        <v>12.22335477</v>
+        <v>12.145041675</v>
       </c>
       <c r="P36">
-        <v>33.04832956333333</v>
+        <v>32.83659415833333</v>
       </c>
       <c r="Q36">
-        <v>74.24832956333333</v>
+        <v>74.03659415833332</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09215399659080342</v>
+        <v>0.09272720848095448</v>
       </c>
       <c r="T36">
-        <v>0.8489897264117683</v>
+        <v>0.8594883034835856</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.590680963531892</v>
+        <v>5.430947221716695</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0744018355126204</v>
+        <v>0.07425657327531054</v>
       </c>
       <c r="C37">
-        <v>300.6546481648342</v>
+        <v>297.8463743721902</v>
       </c>
       <c r="D37">
-        <v>477.3496481648342</v>
+        <v>479.7863743721903</v>
       </c>
       <c r="E37">
-        <v>-166.125</v>
+        <v>-160.88</v>
       </c>
       <c r="F37">
-        <v>183.575</v>
+        <v>188.82</v>
       </c>
       <c r="G37">
         <v>6.88</v>
@@ -4446,28 +4446,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M37">
-        <v>10.1516975</v>
+        <v>10.441746</v>
       </c>
       <c r="N37">
-        <v>44.98163583333333</v>
+        <v>44.69158733333333</v>
       </c>
       <c r="O37">
-        <v>12.145041675</v>
+        <v>12.06672858</v>
       </c>
       <c r="P37">
-        <v>32.83659415833333</v>
+        <v>32.62485875333333</v>
       </c>
       <c r="Q37">
-        <v>74.03659415833332</v>
+        <v>73.82485875333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09272720848095448</v>
+        <v>0.09331833324267273</v>
       </c>
       <c r="T37">
-        <v>0.8594883034835856</v>
+        <v>0.8703149610888973</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.430947221716695</v>
+        <v>5.280087576669009</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07425657327531056</v>
+        <v>0.0741113110380007</v>
       </c>
       <c r="C38">
-        <v>297.84637437219</v>
+        <v>295.0631057303225</v>
       </c>
       <c r="D38">
-        <v>479.78637437219</v>
+        <v>482.2481057303225</v>
       </c>
       <c r="E38">
-        <v>-160.88</v>
+        <v>-155.635</v>
       </c>
       <c r="F38">
-        <v>188.82</v>
+        <v>194.065</v>
       </c>
       <c r="G38">
         <v>6.88</v>
@@ -4528,28 +4528,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M38">
-        <v>10.441746</v>
+        <v>10.7317945</v>
       </c>
       <c r="N38">
-        <v>44.69158733333333</v>
+        <v>44.40153883333333</v>
       </c>
       <c r="O38">
-        <v>12.06672858</v>
+        <v>11.988415485</v>
       </c>
       <c r="P38">
-        <v>32.62485875333333</v>
+        <v>32.41312334833333</v>
       </c>
       <c r="Q38">
-        <v>73.82485875333333</v>
+        <v>73.61312334833332</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09331833324267273</v>
+        <v>0.09392822386984237</v>
       </c>
       <c r="T38">
-        <v>0.8703149610888973</v>
+        <v>0.8814853221102504</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.28008757666901</v>
+        <v>5.137382507029308</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0741113110380007</v>
+        <v>0.07396604880069083</v>
       </c>
       <c r="C39">
-        <v>295.0631057303225</v>
+        <v>292.3052291203494</v>
       </c>
       <c r="D39">
-        <v>482.2481057303225</v>
+        <v>484.7352291203494</v>
       </c>
       <c r="E39">
-        <v>-155.635</v>
+        <v>-150.39</v>
       </c>
       <c r="F39">
-        <v>194.065</v>
+        <v>199.31</v>
       </c>
       <c r="G39">
         <v>6.88</v>
@@ -4610,28 +4610,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M39">
-        <v>10.7317945</v>
+        <v>11.021843</v>
       </c>
       <c r="N39">
-        <v>44.40153883333333</v>
+        <v>44.11149033333334</v>
       </c>
       <c r="O39">
-        <v>11.988415485</v>
+        <v>11.91010239</v>
       </c>
       <c r="P39">
-        <v>32.41312334833333</v>
+        <v>32.20138794333333</v>
       </c>
       <c r="Q39">
-        <v>73.61312334833332</v>
+        <v>73.40138794333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09392822386984237</v>
+        <v>0.09455778838821102</v>
       </c>
       <c r="T39">
-        <v>0.8814853221102504</v>
+        <v>0.8930160173580989</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.137382507029308</v>
+        <v>5.002188230528536</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07396604880069083</v>
+        <v>0.07382078656338098</v>
       </c>
       <c r="C40">
-        <v>292.3052291203494</v>
+        <v>289.5731394458912</v>
       </c>
       <c r="D40">
-        <v>484.7352291203494</v>
+        <v>487.2481394458912</v>
       </c>
       <c r="E40">
-        <v>-150.39</v>
+        <v>-145.145</v>
       </c>
       <c r="F40">
-        <v>199.31</v>
+        <v>204.555</v>
       </c>
       <c r="G40">
         <v>6.88</v>
@@ -4692,28 +4692,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M40">
-        <v>11.021843</v>
+        <v>11.3118915</v>
       </c>
       <c r="N40">
-        <v>44.11149033333334</v>
+        <v>43.82144183333333</v>
       </c>
       <c r="O40">
-        <v>11.91010239</v>
+        <v>11.831789295</v>
       </c>
       <c r="P40">
-        <v>32.20138794333333</v>
+        <v>31.98965253833333</v>
       </c>
       <c r="Q40">
-        <v>73.40138794333333</v>
+        <v>73.18965253833332</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09455778838821102</v>
+        <v>0.09520799436619833</v>
       </c>
       <c r="T40">
-        <v>0.8930160173580989</v>
+        <v>0.9049247681878442</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.002188230528536</v>
+        <v>4.873926993848317</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07382078656338098</v>
+        <v>0.07367552432607112</v>
       </c>
       <c r="C41">
-        <v>289.5731394458912</v>
+        <v>286.8672398421043</v>
       </c>
       <c r="D41">
-        <v>487.2481394458912</v>
+        <v>489.7872398421043</v>
       </c>
       <c r="E41">
-        <v>-145.145</v>
+        <v>-139.9</v>
       </c>
       <c r="F41">
-        <v>204.555</v>
+        <v>209.8</v>
       </c>
       <c r="G41">
         <v>6.88</v>
@@ -4774,28 +4774,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M41">
-        <v>11.3118915</v>
+        <v>11.60194</v>
       </c>
       <c r="N41">
-        <v>43.82144183333333</v>
+        <v>43.53139333333333</v>
       </c>
       <c r="O41">
-        <v>11.831789295</v>
+        <v>11.7534762</v>
       </c>
       <c r="P41">
-        <v>31.98965253833333</v>
+        <v>31.77791713333333</v>
       </c>
       <c r="Q41">
-        <v>73.18965253833332</v>
+        <v>72.97791713333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09520799436619833</v>
+        <v>0.0958798738767852</v>
       </c>
       <c r="T41">
-        <v>0.9049247681878442</v>
+        <v>0.9172304773785809</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.873926993848317</v>
+        <v>4.75207881900211</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07367552432607112</v>
+        <v>0.07353026208876126</v>
       </c>
       <c r="C42">
-        <v>286.8672398421043</v>
+        <v>284.187941891279</v>
       </c>
       <c r="D42">
-        <v>489.7872398421043</v>
+        <v>492.352941891279</v>
       </c>
       <c r="E42">
-        <v>-139.9</v>
+        <v>-134.655</v>
       </c>
       <c r="F42">
-        <v>209.8</v>
+        <v>215.045</v>
       </c>
       <c r="G42">
         <v>6.88</v>
@@ -4856,28 +4856,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M42">
-        <v>11.60194</v>
+        <v>11.8919885</v>
       </c>
       <c r="N42">
-        <v>43.53139333333333</v>
+        <v>43.24134483333333</v>
       </c>
       <c r="O42">
-        <v>11.7534762</v>
+        <v>11.675163105</v>
       </c>
       <c r="P42">
-        <v>31.77791713333333</v>
+        <v>31.56618172833333</v>
       </c>
       <c r="Q42">
-        <v>72.97791713333334</v>
+        <v>72.76618172833332</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0958798738767852</v>
+        <v>0.09657452896400215</v>
       </c>
       <c r="T42">
-        <v>0.9172304773785809</v>
+        <v>0.9299533292537493</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.75207881900211</v>
+        <v>4.636174457563033</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07353026208876126</v>
+        <v>0.07338499985145142</v>
       </c>
       <c r="C43">
-        <v>284.187941891279</v>
+        <v>281.5356658452524</v>
       </c>
       <c r="D43">
-        <v>492.352941891279</v>
+        <v>494.9456658452524</v>
       </c>
       <c r="E43">
-        <v>-134.655</v>
+        <v>-129.41</v>
       </c>
       <c r="F43">
-        <v>215.045</v>
+        <v>220.29</v>
       </c>
       <c r="G43">
         <v>6.88</v>
@@ -4938,28 +4938,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M43">
-        <v>11.8919885</v>
+        <v>12.182037</v>
       </c>
       <c r="N43">
-        <v>43.24134483333333</v>
+        <v>42.95129633333333</v>
       </c>
       <c r="O43">
-        <v>11.675163105</v>
+        <v>11.59685001</v>
       </c>
       <c r="P43">
-        <v>31.56618172833333</v>
+        <v>31.35444632333333</v>
       </c>
       <c r="Q43">
-        <v>72.76618172833332</v>
+        <v>72.55444632333332</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09657452896400215</v>
+        <v>0.09729313767491624</v>
       </c>
       <c r="T43">
-        <v>0.9299533292537493</v>
+        <v>0.943114900159096</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.636174457563033</v>
+        <v>4.52578935143058</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07338499985145142</v>
+        <v>0.07402448761414156</v>
       </c>
       <c r="C44">
-        <v>281.5356658452524</v>
+        <v>265.0765846250152</v>
       </c>
       <c r="D44">
-        <v>494.9456658452524</v>
+        <v>483.7315846250152</v>
       </c>
       <c r="E44">
-        <v>-129.41</v>
+        <v>-124.165</v>
       </c>
       <c r="F44">
-        <v>220.29</v>
+        <v>225.535</v>
       </c>
       <c r="G44">
         <v>6.88</v>
@@ -5020,45 +5020,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M44">
-        <v>12.182037</v>
+        <v>13.035923</v>
       </c>
       <c r="N44">
-        <v>42.95129633333333</v>
+        <v>42.09741033333333</v>
       </c>
       <c r="O44">
-        <v>11.59685001</v>
+        <v>11.36630079</v>
       </c>
       <c r="P44">
-        <v>31.35444632333333</v>
+        <v>30.73110954333333</v>
       </c>
       <c r="Q44">
-        <v>72.55444632333332</v>
+        <v>71.93110954333332</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09729313767491621</v>
+        <v>0.09803696072656412</v>
       </c>
       <c r="T44">
-        <v>0.9431149001590957</v>
+        <v>0.9567382805698933</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.52578935143058</v>
+        <v>4.229338676926316</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07402448761414156</v>
+        <v>0.07389747537683169</v>
       </c>
       <c r="C45">
-        <v>265.0765846250152</v>
+        <v>262.0182519321901</v>
       </c>
       <c r="D45">
-        <v>483.7315846250152</v>
+        <v>485.9182519321901</v>
       </c>
       <c r="E45">
-        <v>-124.165</v>
+        <v>-118.92</v>
       </c>
       <c r="F45">
-        <v>225.535</v>
+        <v>230.78</v>
       </c>
       <c r="G45">
         <v>6.88</v>
@@ -5102,28 +5102,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M45">
-        <v>13.035923</v>
+        <v>13.339084</v>
       </c>
       <c r="N45">
-        <v>42.09741033333333</v>
+        <v>41.79424933333333</v>
       </c>
       <c r="O45">
-        <v>11.36630079</v>
+        <v>11.28444732</v>
       </c>
       <c r="P45">
-        <v>30.73110954333333</v>
+        <v>30.50980201333333</v>
       </c>
       <c r="Q45">
-        <v>71.93110954333332</v>
+        <v>71.70980201333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09803696072656412</v>
+        <v>0.09880734888719944</v>
       </c>
       <c r="T45">
-        <v>0.9567382805698933</v>
+        <v>0.9708482102810763</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.229338676926316</v>
+        <v>4.133217343359808</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07389747537683169</v>
+        <v>0.07377046313952185</v>
       </c>
       <c r="C46">
-        <v>262.0182519321901</v>
+        <v>258.9797782960811</v>
       </c>
       <c r="D46">
-        <v>485.9182519321901</v>
+        <v>488.1247782960811</v>
       </c>
       <c r="E46">
-        <v>-118.92</v>
+        <v>-113.675</v>
       </c>
       <c r="F46">
-        <v>230.78</v>
+        <v>236.025</v>
       </c>
       <c r="G46">
         <v>6.88</v>
@@ -5184,28 +5184,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M46">
-        <v>13.339084</v>
+        <v>13.642245</v>
       </c>
       <c r="N46">
-        <v>41.79424933333333</v>
+        <v>41.49108833333333</v>
       </c>
       <c r="O46">
-        <v>11.28444732</v>
+        <v>11.20259385</v>
       </c>
       <c r="P46">
-        <v>30.50980201333333</v>
+        <v>30.28849448333333</v>
       </c>
       <c r="Q46">
-        <v>71.70980201333333</v>
+        <v>71.48849448333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09880734888719944</v>
+        <v>0.09960575116276699</v>
       </c>
       <c r="T46">
-        <v>0.9708482102810763</v>
+        <v>0.9854712283453932</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.133217343359808</v>
+        <v>4.041368069062924</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07377046313952185</v>
+        <v>0.07481875090221199</v>
       </c>
       <c r="C47">
-        <v>258.9797782960811</v>
+        <v>236.1015164965659</v>
       </c>
       <c r="D47">
-        <v>488.1247782960811</v>
+        <v>470.491516496566</v>
       </c>
       <c r="E47">
-        <v>-113.675</v>
+        <v>-108.43</v>
       </c>
       <c r="F47">
-        <v>236.025</v>
+        <v>241.27</v>
       </c>
       <c r="G47">
         <v>6.88</v>
@@ -5266,45 +5266,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M47">
-        <v>13.642245</v>
+        <v>14.789851</v>
       </c>
       <c r="N47">
-        <v>41.49108833333333</v>
+        <v>40.34348233333333</v>
       </c>
       <c r="O47">
-        <v>11.20259385</v>
+        <v>10.89274023</v>
       </c>
       <c r="P47">
-        <v>30.28849448333333</v>
+        <v>29.45074210333333</v>
       </c>
       <c r="Q47">
-        <v>71.48849448333333</v>
+        <v>70.65074210333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09960575116276699</v>
+        <v>0.1004337238929852</v>
       </c>
       <c r="T47">
-        <v>0.9854712283453932</v>
+        <v>1.000635839671352</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.041368069062924</v>
+        <v>3.727781526219117</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07481875090221199</v>
+        <v>0.07471728866490213</v>
       </c>
       <c r="C48">
-        <v>236.1015164965659</v>
+        <v>232.5073324652494</v>
       </c>
       <c r="D48">
-        <v>470.491516496566</v>
+        <v>472.1423324652495</v>
       </c>
       <c r="E48">
-        <v>-108.43</v>
+        <v>-103.185</v>
       </c>
       <c r="F48">
-        <v>241.27</v>
+        <v>246.515</v>
       </c>
       <c r="G48">
         <v>6.88</v>
@@ -5348,28 +5348,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M48">
-        <v>14.789851</v>
+        <v>15.1113695</v>
       </c>
       <c r="N48">
-        <v>40.34348233333333</v>
+        <v>40.02196383333333</v>
       </c>
       <c r="O48">
-        <v>10.89274023</v>
+        <v>10.805930235</v>
       </c>
       <c r="P48">
-        <v>29.45074210333333</v>
+        <v>29.21603359833333</v>
       </c>
       <c r="Q48">
-        <v>70.65074210333333</v>
+        <v>70.41603359833333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1004337238929852</v>
+        <v>0.1012929408771738</v>
       </c>
       <c r="T48">
-        <v>1.000635839671352</v>
+        <v>1.016372700481308</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.727781526219117</v>
+        <v>3.648467025661263</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07471728866490213</v>
+        <v>0.07461582642759228</v>
       </c>
       <c r="C49">
-        <v>232.5073324652494</v>
+        <v>228.9247736761926</v>
       </c>
       <c r="D49">
-        <v>472.1423324652495</v>
+        <v>473.8047736761927</v>
       </c>
       <c r="E49">
-        <v>-103.185</v>
+        <v>-97.93999999999997</v>
       </c>
       <c r="F49">
-        <v>246.515</v>
+        <v>251.76</v>
       </c>
       <c r="G49">
         <v>6.88</v>
@@ -5430,28 +5430,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M49">
-        <v>15.1113695</v>
+        <v>15.432888</v>
       </c>
       <c r="N49">
-        <v>40.02196383333333</v>
+        <v>39.70044533333333</v>
       </c>
       <c r="O49">
-        <v>10.805930235</v>
+        <v>10.71912024</v>
       </c>
       <c r="P49">
-        <v>29.21603359833333</v>
+        <v>28.98132509333333</v>
       </c>
       <c r="Q49">
-        <v>70.41603359833333</v>
+        <v>70.18132509333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1012929408771738</v>
+        <v>0.1021852046684467</v>
       </c>
       <c r="T49">
-        <v>1.016372700481308</v>
+        <v>1.032714825168571</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.648467025661263</v>
+        <v>3.572457295959987</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07461582642759228</v>
+        <v>0.07551592419028241</v>
       </c>
       <c r="C50">
-        <v>228.9247736761927</v>
+        <v>209.3281885123932</v>
       </c>
       <c r="D50">
-        <v>473.8047736761927</v>
+        <v>459.4531885123932</v>
       </c>
       <c r="E50">
-        <v>-97.94</v>
+        <v>-92.69499999999999</v>
       </c>
       <c r="F50">
-        <v>251.76</v>
+        <v>257.005</v>
       </c>
       <c r="G50">
         <v>6.88</v>
@@ -5512,45 +5512,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M50">
-        <v>15.432888</v>
+        <v>16.4740205</v>
       </c>
       <c r="N50">
-        <v>39.70044533333333</v>
+        <v>38.65931283333333</v>
       </c>
       <c r="O50">
-        <v>10.71912024</v>
+        <v>10.438014465</v>
       </c>
       <c r="P50">
-        <v>28.98132509333333</v>
+        <v>28.22129836833333</v>
       </c>
       <c r="Q50">
-        <v>70.18132509333333</v>
+        <v>69.42129836833332</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1021852046684467</v>
+        <v>0.1031124591966322</v>
       </c>
       <c r="T50">
-        <v>1.032714825168571</v>
+        <v>1.049697817490628</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.572457295959987</v>
+        <v>3.346683545363642</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07551592419028241</v>
+        <v>0.07543490195297256</v>
       </c>
       <c r="C51">
-        <v>209.3281885123932</v>
+        <v>205.3393399696004</v>
       </c>
       <c r="D51">
-        <v>459.4531885123932</v>
+        <v>460.7093399696004</v>
       </c>
       <c r="E51">
-        <v>-92.69499999999999</v>
+        <v>-87.44999999999999</v>
       </c>
       <c r="F51">
-        <v>257.005</v>
+        <v>262.25</v>
       </c>
       <c r="G51">
         <v>6.88</v>
@@ -5594,28 +5594,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M51">
-        <v>16.4740205</v>
+        <v>16.810225</v>
       </c>
       <c r="N51">
-        <v>38.65931283333333</v>
+        <v>38.32310833333333</v>
       </c>
       <c r="O51">
-        <v>10.438014465</v>
+        <v>10.34723925</v>
       </c>
       <c r="P51">
-        <v>28.22129836833333</v>
+        <v>27.97586908333333</v>
       </c>
       <c r="Q51">
-        <v>69.42129836833332</v>
+        <v>69.17586908333332</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1031124591966322</v>
+        <v>0.1040768039059451</v>
       </c>
       <c r="T51">
-        <v>1.049697817490628</v>
+        <v>1.067360129505568</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.346683545363642</v>
+        <v>3.279749874456369</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07543490195297256</v>
+        <v>0.07535387971566271</v>
       </c>
       <c r="C52">
-        <v>205.3393399696004</v>
+        <v>201.3573789287154</v>
       </c>
       <c r="D52">
-        <v>460.7093399696004</v>
+        <v>461.9723789287154</v>
       </c>
       <c r="E52">
-        <v>-87.44999999999999</v>
+        <v>-82.20499999999998</v>
       </c>
       <c r="F52">
-        <v>262.25</v>
+        <v>267.495</v>
       </c>
       <c r="G52">
         <v>6.88</v>
@@ -5676,28 +5676,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M52">
-        <v>16.810225</v>
+        <v>17.1464295</v>
       </c>
       <c r="N52">
-        <v>38.32310833333333</v>
+        <v>37.98690383333333</v>
       </c>
       <c r="O52">
-        <v>10.34723925</v>
+        <v>10.256464035</v>
       </c>
       <c r="P52">
-        <v>27.97586908333333</v>
+        <v>27.73043979833333</v>
       </c>
       <c r="Q52">
-        <v>69.17586908333332</v>
+        <v>68.93043979833332</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1040768039059451</v>
+        <v>0.1050805096238014</v>
       </c>
       <c r="T52">
-        <v>1.067360129505568</v>
+        <v>1.085743352214995</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.279749874456369</v>
+        <v>3.215441053388598</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07535387971566271</v>
+        <v>0.07527285747835284</v>
       </c>
       <c r="C53">
-        <v>201.3573789287154</v>
+        <v>197.3823621919147</v>
       </c>
       <c r="D53">
-        <v>461.9723789287154</v>
+        <v>463.2423621919147</v>
       </c>
       <c r="E53">
-        <v>-82.20499999999998</v>
+        <v>-76.95999999999998</v>
       </c>
       <c r="F53">
-        <v>267.495</v>
+        <v>272.74</v>
       </c>
       <c r="G53">
         <v>6.88</v>
@@ -5758,28 +5758,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M53">
-        <v>17.1464295</v>
+        <v>17.482634</v>
       </c>
       <c r="N53">
-        <v>37.98690383333333</v>
+        <v>37.65069933333334</v>
       </c>
       <c r="O53">
-        <v>10.256464035</v>
+        <v>10.16568882</v>
       </c>
       <c r="P53">
-        <v>27.73043979833333</v>
+        <v>27.48501051333334</v>
       </c>
       <c r="Q53">
-        <v>68.93043979833332</v>
+        <v>68.68501051333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1050805096238014</v>
+        <v>0.1061260364132351</v>
       </c>
       <c r="T53">
-        <v>1.085743352214995</v>
+        <v>1.104892542537315</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.215441053388598</v>
+        <v>3.15360564851574</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07527285747835284</v>
+        <v>0.07519183524104299</v>
       </c>
       <c r="C54">
-        <v>197.3823621919147</v>
+        <v>193.4143471877029</v>
       </c>
       <c r="D54">
-        <v>463.2423621919147</v>
+        <v>464.5193471877029</v>
       </c>
       <c r="E54">
-        <v>-76.95999999999998</v>
+        <v>-71.71499999999997</v>
       </c>
       <c r="F54">
-        <v>272.74</v>
+        <v>277.985</v>
       </c>
       <c r="G54">
         <v>6.88</v>
@@ -5840,28 +5840,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M54">
-        <v>17.482634</v>
+        <v>17.8188385</v>
       </c>
       <c r="N54">
-        <v>37.65069933333334</v>
+        <v>37.31449483333333</v>
       </c>
       <c r="O54">
-        <v>10.16568882</v>
+        <v>10.074913605</v>
       </c>
       <c r="P54">
-        <v>27.48501051333334</v>
+        <v>27.23958122833333</v>
       </c>
       <c r="Q54">
-        <v>68.68501051333334</v>
+        <v>68.43958122833332</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1061260364132351</v>
+        <v>0.1072160537043468</v>
       </c>
       <c r="T54">
-        <v>1.104892542537315</v>
+        <v>1.124856592022287</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.15360564851574</v>
+        <v>3.094103655147519</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07519183524104299</v>
+        <v>0.07511081300373312</v>
       </c>
       <c r="C55">
-        <v>193.4143471877029</v>
+        <v>189.4533919795711</v>
       </c>
       <c r="D55">
-        <v>464.5193471877029</v>
+        <v>465.8033919795711</v>
       </c>
       <c r="E55">
-        <v>-71.71499999999997</v>
+        <v>-66.46999999999997</v>
       </c>
       <c r="F55">
-        <v>277.985</v>
+        <v>283.23</v>
       </c>
       <c r="G55">
         <v>6.88</v>
@@ -5922,28 +5922,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M55">
-        <v>17.8188385</v>
+        <v>18.155043</v>
       </c>
       <c r="N55">
-        <v>37.31449483333333</v>
+        <v>36.97829033333333</v>
       </c>
       <c r="O55">
-        <v>10.074913605</v>
+        <v>9.98413839</v>
       </c>
       <c r="P55">
-        <v>27.23958122833333</v>
+        <v>26.99415194333334</v>
       </c>
       <c r="Q55">
-        <v>68.43958122833332</v>
+        <v>68.19415194333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1072160537043468</v>
+        <v>0.1083534630515938</v>
       </c>
       <c r="T55">
-        <v>1.124856592022287</v>
+        <v>1.145688643658779</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.094103655147519</v>
+        <v>3.036805439311454</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07511081300373312</v>
+        <v>0.07816149076642329</v>
       </c>
       <c r="C56">
-        <v>189.4533919795711</v>
+        <v>140.2976815628525</v>
       </c>
       <c r="D56">
-        <v>465.8033919795711</v>
+        <v>421.8926815628525</v>
       </c>
       <c r="E56">
-        <v>-66.46999999999997</v>
+        <v>-61.22499999999997</v>
       </c>
       <c r="F56">
-        <v>283.23</v>
+        <v>288.475</v>
       </c>
       <c r="G56">
         <v>6.88</v>
@@ -6004,45 +6004,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M56">
-        <v>18.155043</v>
+        <v>20.7413525</v>
       </c>
       <c r="N56">
-        <v>36.97829033333333</v>
+        <v>34.39198083333333</v>
       </c>
       <c r="O56">
-        <v>9.98413839</v>
+        <v>9.285834824999998</v>
       </c>
       <c r="P56">
-        <v>26.99415194333334</v>
+        <v>25.10614600833333</v>
       </c>
       <c r="Q56">
-        <v>68.19415194333334</v>
+        <v>66.30614600833333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1083534630515938</v>
+        <v>0.1095414239253851</v>
       </c>
       <c r="T56">
-        <v>1.145688643658779</v>
+        <v>1.167446564256893</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.036805439311454</v>
+        <v>2.658135882572427</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07816149076642329</v>
+        <v>0.07813740852911341</v>
       </c>
       <c r="C57">
-        <v>140.2976815628525</v>
+        <v>135.3668724686435</v>
       </c>
       <c r="D57">
-        <v>421.8926815628525</v>
+        <v>422.2068724686435</v>
       </c>
       <c r="E57">
-        <v>-61.22499999999997</v>
+        <v>-55.97999999999996</v>
       </c>
       <c r="F57">
-        <v>288.475</v>
+        <v>293.72</v>
       </c>
       <c r="G57">
         <v>6.88</v>
@@ -6086,28 +6086,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M57">
-        <v>20.7413525</v>
+        <v>21.118468</v>
       </c>
       <c r="N57">
-        <v>34.39198083333333</v>
+        <v>34.01486533333333</v>
       </c>
       <c r="O57">
-        <v>9.285834824999998</v>
+        <v>9.18401364</v>
       </c>
       <c r="P57">
-        <v>25.10614600833333</v>
+        <v>24.83085169333333</v>
       </c>
       <c r="Q57">
-        <v>66.30614600833333</v>
+        <v>66.03085169333333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1095414239253851</v>
+        <v>0.1107833830207123</v>
       </c>
       <c r="T57">
-        <v>1.167446564256893</v>
+        <v>1.190193481245831</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.658135882572427</v>
+        <v>2.610669170383634</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07813740852911341</v>
+        <v>0.07811332629180356</v>
       </c>
       <c r="C58">
-        <v>135.3668724686435</v>
+        <v>130.4365316901925</v>
       </c>
       <c r="D58">
-        <v>422.2068724686435</v>
+        <v>422.5215316901925</v>
       </c>
       <c r="E58">
-        <v>-55.97999999999996</v>
+        <v>-50.73499999999996</v>
       </c>
       <c r="F58">
-        <v>293.72</v>
+        <v>298.965</v>
       </c>
       <c r="G58">
         <v>6.88</v>
@@ -6168,28 +6168,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M58">
-        <v>21.118468</v>
+        <v>21.49558350000001</v>
       </c>
       <c r="N58">
-        <v>34.01486533333333</v>
+        <v>33.63774983333333</v>
       </c>
       <c r="O58">
-        <v>9.18401364</v>
+        <v>9.082192454999999</v>
       </c>
       <c r="P58">
-        <v>24.83085169333333</v>
+        <v>24.55555737833333</v>
       </c>
       <c r="Q58">
-        <v>66.03085169333333</v>
+        <v>65.75555737833332</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1107833830207123</v>
+        <v>0.1120831076553571</v>
       </c>
       <c r="T58">
-        <v>1.190193481245831</v>
+        <v>1.213998394373789</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.610669170383634</v>
+        <v>2.564867956868132</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07811332629180356</v>
+        <v>0.07808924405449372</v>
       </c>
       <c r="C59">
-        <v>130.4365316901925</v>
+        <v>125.5066602753495</v>
       </c>
       <c r="D59">
-        <v>422.5215316901925</v>
+        <v>422.8366602753496</v>
       </c>
       <c r="E59">
-        <v>-50.73499999999996</v>
+        <v>-45.48999999999995</v>
       </c>
       <c r="F59">
-        <v>298.965</v>
+        <v>304.21</v>
       </c>
       <c r="G59">
         <v>6.88</v>
@@ -6250,28 +6250,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M59">
-        <v>21.49558350000001</v>
+        <v>21.872699</v>
       </c>
       <c r="N59">
-        <v>33.63774983333333</v>
+        <v>33.26063433333333</v>
       </c>
       <c r="O59">
-        <v>9.082192454999999</v>
+        <v>8.980371269999999</v>
       </c>
       <c r="P59">
-        <v>24.55555737833333</v>
+        <v>24.28026306333333</v>
       </c>
       <c r="Q59">
-        <v>65.75555737833332</v>
+        <v>65.48026306333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1120831076553571</v>
+        <v>0.1134447239392707</v>
       </c>
       <c r="T59">
-        <v>1.213998394373789</v>
+        <v>1.238936874793554</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.564867956868132</v>
+        <v>2.520646095542819</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0780892440544937</v>
+        <v>0.07974489181718386</v>
       </c>
       <c r="C60">
-        <v>125.5066602753498</v>
+        <v>99.63798074387256</v>
       </c>
       <c r="D60">
-        <v>422.8366602753497</v>
+        <v>402.2129807438725</v>
       </c>
       <c r="E60">
-        <v>-45.49000000000001</v>
+        <v>-40.245</v>
       </c>
       <c r="F60">
-        <v>304.21</v>
+        <v>309.455</v>
       </c>
       <c r="G60">
         <v>6.88</v>
@@ -6332,45 +6332,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M60">
-        <v>21.872699</v>
+        <v>23.456689</v>
       </c>
       <c r="N60">
-        <v>33.26063433333333</v>
+        <v>31.67664433333333</v>
       </c>
       <c r="O60">
-        <v>8.980371269999999</v>
+        <v>8.55269397</v>
       </c>
       <c r="P60">
-        <v>24.28026306333333</v>
+        <v>23.12395036333333</v>
       </c>
       <c r="Q60">
-        <v>65.48026306333333</v>
+        <v>64.32395036333332</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1134447239392707</v>
+        <v>0.1148727605297167</v>
       </c>
       <c r="T60">
-        <v>1.238936874793554</v>
+        <v>1.265091866453308</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.27</v>
       </c>
       <c r="W60">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.520646095542819</v>
+        <v>2.350431185464126</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07974489181718386</v>
+        <v>0.07974927957987399</v>
       </c>
       <c r="C61">
-        <v>99.63798074387256</v>
+        <v>94.34099686874379</v>
       </c>
       <c r="D61">
-        <v>402.2129807438725</v>
+        <v>402.1609968687438</v>
       </c>
       <c r="E61">
-        <v>-40.245</v>
+        <v>-35</v>
       </c>
       <c r="F61">
-        <v>309.455</v>
+        <v>314.7</v>
       </c>
       <c r="G61">
         <v>6.88</v>
@@ -6414,28 +6414,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M61">
-        <v>23.456689</v>
+        <v>23.85426</v>
       </c>
       <c r="N61">
-        <v>31.67664433333333</v>
+        <v>31.27907333333333</v>
       </c>
       <c r="O61">
-        <v>8.55269397</v>
+        <v>8.445349800000001</v>
       </c>
       <c r="P61">
-        <v>23.12395036333333</v>
+        <v>22.83372353333333</v>
       </c>
       <c r="Q61">
-        <v>64.32395036333332</v>
+        <v>64.03372353333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1148727605297167</v>
+        <v>0.116372198949685</v>
       </c>
       <c r="T61">
-        <v>1.265091866453308</v>
+        <v>1.292554607696049</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.350431185464126</v>
+        <v>2.311257332373057</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07974927957987399</v>
+        <v>0.07975366734256413</v>
       </c>
       <c r="C62">
-        <v>94.34099686874379</v>
+        <v>89.04402642915363</v>
       </c>
       <c r="D62">
-        <v>402.1609968687438</v>
+        <v>402.1090264291536</v>
       </c>
       <c r="E62">
-        <v>-35</v>
+        <v>-29.755</v>
       </c>
       <c r="F62">
-        <v>314.7</v>
+        <v>319.945</v>
       </c>
       <c r="G62">
         <v>6.88</v>
@@ -6496,28 +6496,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M62">
-        <v>23.85426</v>
+        <v>24.251831</v>
       </c>
       <c r="N62">
-        <v>31.27907333333333</v>
+        <v>30.88150233333333</v>
       </c>
       <c r="O62">
-        <v>8.445349800000001</v>
+        <v>8.33800563</v>
       </c>
       <c r="P62">
-        <v>22.83372353333333</v>
+        <v>22.54349670333333</v>
       </c>
       <c r="Q62">
-        <v>64.03372353333333</v>
+        <v>63.74349670333333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.116372198949685</v>
+        <v>0.1179485316476003</v>
       </c>
       <c r="T62">
-        <v>1.292554607696049</v>
+        <v>1.321425694643547</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.311257332373057</v>
+        <v>2.273367867907925</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07975366734256413</v>
+        <v>0.07975805510525429</v>
       </c>
       <c r="C63">
-        <v>89.04402642915363</v>
+        <v>83.74706941989405</v>
       </c>
       <c r="D63">
-        <v>402.1090264291536</v>
+        <v>402.057069419894</v>
       </c>
       <c r="E63">
-        <v>-29.755</v>
+        <v>-24.50999999999999</v>
       </c>
       <c r="F63">
-        <v>319.945</v>
+        <v>325.19</v>
       </c>
       <c r="G63">
         <v>6.88</v>
@@ -6578,28 +6578,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M63">
-        <v>24.251831</v>
+        <v>24.649402</v>
       </c>
       <c r="N63">
-        <v>30.88150233333333</v>
+        <v>30.48393133333333</v>
       </c>
       <c r="O63">
-        <v>8.33800563</v>
+        <v>8.23066146</v>
       </c>
       <c r="P63">
-        <v>22.54349670333333</v>
+        <v>22.25326987333333</v>
       </c>
       <c r="Q63">
-        <v>63.74349670333333</v>
+        <v>63.45326987333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1179485316476003</v>
+        <v>0.1196078292243534</v>
       </c>
       <c r="T63">
-        <v>1.321425694643547</v>
+        <v>1.351816312483018</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.273367867907925</v>
+        <v>2.236700644231991</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07975805510525429</v>
+        <v>0.07976244286794443</v>
       </c>
       <c r="C64">
-        <v>83.74706941989405</v>
+        <v>78.45012583576005</v>
       </c>
       <c r="D64">
-        <v>402.057069419894</v>
+        <v>402.0051258357601</v>
       </c>
       <c r="E64">
-        <v>-24.50999999999999</v>
+        <v>-19.26499999999999</v>
       </c>
       <c r="F64">
-        <v>325.19</v>
+        <v>330.435</v>
       </c>
       <c r="G64">
         <v>6.88</v>
@@ -6660,28 +6660,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M64">
-        <v>24.649402</v>
+        <v>25.046973</v>
       </c>
       <c r="N64">
-        <v>30.48393133333333</v>
+        <v>30.08636033333333</v>
       </c>
       <c r="O64">
-        <v>8.23066146</v>
+        <v>8.123317289999999</v>
       </c>
       <c r="P64">
-        <v>22.25326987333333</v>
+        <v>21.96304304333333</v>
       </c>
       <c r="Q64">
-        <v>63.45326987333333</v>
+        <v>63.16304304333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1196078292243534</v>
+        <v>0.1213568185620119</v>
       </c>
       <c r="T64">
-        <v>1.351816312483018</v>
+        <v>1.38384966642192</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.236700644231991</v>
+        <v>2.201197459402912</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07976244286794443</v>
+        <v>0.07976683063063457</v>
       </c>
       <c r="C65">
-        <v>78.45012583576005</v>
+        <v>73.15319567154864</v>
       </c>
       <c r="D65">
-        <v>402.0051258357601</v>
+        <v>401.9531956715487</v>
       </c>
       <c r="E65">
-        <v>-19.26499999999999</v>
+        <v>-14.01999999999998</v>
       </c>
       <c r="F65">
-        <v>330.435</v>
+        <v>335.68</v>
       </c>
       <c r="G65">
         <v>6.88</v>
@@ -6742,28 +6742,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M65">
-        <v>25.046973</v>
+        <v>25.444544</v>
       </c>
       <c r="N65">
-        <v>30.08636033333333</v>
+        <v>29.68878933333333</v>
       </c>
       <c r="O65">
-        <v>8.123317289999999</v>
+        <v>8.01597312</v>
       </c>
       <c r="P65">
-        <v>21.96304304333333</v>
+        <v>21.67281621333333</v>
       </c>
       <c r="Q65">
-        <v>63.16304304333333</v>
+        <v>62.87281621333332</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1213568185620119</v>
+        <v>0.1232029739739849</v>
       </c>
       <c r="T65">
-        <v>1.38384966642192</v>
+        <v>1.417662651135206</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.201197459402912</v>
+        <v>2.166803749099741</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07976683063063457</v>
+        <v>0.07977121839332471</v>
       </c>
       <c r="C66">
-        <v>73.15319567154864</v>
+        <v>67.85627892206003</v>
       </c>
       <c r="D66">
-        <v>401.9531956715487</v>
+        <v>401.90127892206</v>
       </c>
       <c r="E66">
-        <v>-14.01999999999998</v>
+        <v>-8.774999999999977</v>
       </c>
       <c r="F66">
-        <v>335.68</v>
+        <v>340.925</v>
       </c>
       <c r="G66">
         <v>6.88</v>
@@ -6824,28 +6824,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M66">
-        <v>25.444544</v>
+        <v>25.842115</v>
       </c>
       <c r="N66">
-        <v>29.68878933333333</v>
+        <v>29.29121833333333</v>
       </c>
       <c r="O66">
-        <v>8.01597312</v>
+        <v>7.90862895</v>
       </c>
       <c r="P66">
-        <v>21.67281621333333</v>
+        <v>21.38258938333333</v>
       </c>
       <c r="Q66">
-        <v>62.87281621333332</v>
+        <v>62.58258938333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1232029739739849</v>
+        <v>0.1251546239809277</v>
       </c>
       <c r="T66">
-        <v>1.417662651135206</v>
+        <v>1.453407806403536</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.166803749099741</v>
+        <v>2.133468306805899</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07977121839332471</v>
+        <v>0.07977560615601484</v>
       </c>
       <c r="C67">
-        <v>67.85627892206003</v>
+        <v>62.55937558209683</v>
       </c>
       <c r="D67">
-        <v>401.90127892206</v>
+        <v>401.8493755820969</v>
       </c>
       <c r="E67">
-        <v>-8.774999999999977</v>
+        <v>-3.529999999999973</v>
       </c>
       <c r="F67">
-        <v>340.925</v>
+        <v>346.17</v>
       </c>
       <c r="G67">
         <v>6.88</v>
@@ -6906,28 +6906,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M67">
-        <v>25.842115</v>
+        <v>26.239686</v>
       </c>
       <c r="N67">
-        <v>29.29121833333333</v>
+        <v>28.89364733333333</v>
       </c>
       <c r="O67">
-        <v>7.90862895</v>
+        <v>7.80128478</v>
       </c>
       <c r="P67">
-        <v>21.38258938333333</v>
+        <v>21.09236255333333</v>
       </c>
       <c r="Q67">
-        <v>62.58258938333333</v>
+        <v>62.29236255333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1251546239809277</v>
+        <v>0.1272210769294554</v>
       </c>
       <c r="T67">
-        <v>1.453407806403536</v>
+        <v>1.491255617864121</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.133468306805899</v>
+        <v>2.101143029430052</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07977560615601484</v>
+        <v>0.07977999391870499</v>
       </c>
       <c r="C68">
-        <v>62.55937558209683</v>
+        <v>57.2624856464642</v>
       </c>
       <c r="D68">
-        <v>401.8493755820969</v>
+        <v>401.7974856464642</v>
       </c>
       <c r="E68">
-        <v>-3.529999999999973</v>
+        <v>1.715000000000032</v>
       </c>
       <c r="F68">
-        <v>346.17</v>
+        <v>351.415</v>
       </c>
       <c r="G68">
         <v>6.88</v>
@@ -6988,28 +6988,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M68">
-        <v>26.239686</v>
+        <v>26.63725700000001</v>
       </c>
       <c r="N68">
-        <v>28.89364733333333</v>
+        <v>28.49607633333333</v>
       </c>
       <c r="O68">
-        <v>7.80128478</v>
+        <v>7.693940609999999</v>
       </c>
       <c r="P68">
-        <v>21.09236255333333</v>
+        <v>20.80213572333333</v>
       </c>
       <c r="Q68">
-        <v>62.29236255333333</v>
+        <v>62.00213572333332</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1272210769294554</v>
+        <v>0.1294127694506212</v>
       </c>
       <c r="T68">
-        <v>1.491255617864121</v>
+        <v>1.531397236079893</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.101143029430052</v>
+        <v>2.069782685707215</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07977999391870499</v>
+        <v>0.07978438168139515</v>
       </c>
       <c r="C69">
-        <v>57.2624856464642</v>
+        <v>51.96560910997027</v>
       </c>
       <c r="D69">
-        <v>401.7974856464642</v>
+        <v>401.7456091099703</v>
       </c>
       <c r="E69">
-        <v>1.715000000000032</v>
+        <v>6.960000000000036</v>
       </c>
       <c r="F69">
-        <v>351.415</v>
+        <v>356.66</v>
       </c>
       <c r="G69">
         <v>6.88</v>
@@ -7070,28 +7070,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M69">
-        <v>26.63725700000001</v>
+        <v>27.034828</v>
       </c>
       <c r="N69">
-        <v>28.49607633333333</v>
+        <v>28.09850533333333</v>
       </c>
       <c r="O69">
-        <v>7.693940609999999</v>
+        <v>7.586596439999999</v>
       </c>
       <c r="P69">
-        <v>20.80213572333333</v>
+        <v>20.51190889333333</v>
       </c>
       <c r="Q69">
-        <v>62.00213572333332</v>
+        <v>61.71190889333332</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1294127694506212</v>
+        <v>0.1317414427543598</v>
       </c>
       <c r="T69">
-        <v>1.531397236079893</v>
+        <v>1.574047705434151</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.069782685707215</v>
+        <v>2.039344705035051</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07978438168139515</v>
+        <v>0.07978876944408528</v>
       </c>
       <c r="C70">
-        <v>51.96560910997027</v>
+        <v>46.66874596742616</v>
       </c>
       <c r="D70">
-        <v>401.7456091099703</v>
+        <v>401.6937459674262</v>
       </c>
       <c r="E70">
-        <v>6.960000000000036</v>
+        <v>12.20500000000004</v>
       </c>
       <c r="F70">
-        <v>356.66</v>
+        <v>361.905</v>
       </c>
       <c r="G70">
         <v>6.88</v>
@@ -7152,28 +7152,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M70">
-        <v>27.034828</v>
+        <v>27.432399</v>
       </c>
       <c r="N70">
-        <v>28.09850533333333</v>
+        <v>27.70093433333333</v>
       </c>
       <c r="O70">
-        <v>7.586596439999999</v>
+        <v>7.479252269999999</v>
       </c>
       <c r="P70">
-        <v>20.51190889333333</v>
+        <v>20.22168206333333</v>
       </c>
       <c r="Q70">
-        <v>61.71190889333332</v>
+        <v>61.42168206333332</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1317414427543598</v>
+        <v>0.1342203530454364</v>
       </c>
       <c r="T70">
-        <v>1.574047705434151</v>
+        <v>1.619449817972554</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.039344705035051</v>
+        <v>2.009788984672224</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07978876944408528</v>
+        <v>0.08704935720677542</v>
       </c>
       <c r="C71">
-        <v>46.66874596742616</v>
+        <v>-29.28117875904212</v>
       </c>
       <c r="D71">
-        <v>401.6937459674262</v>
+        <v>330.9888212409579</v>
       </c>
       <c r="E71">
-        <v>12.20500000000004</v>
+        <v>17.45000000000005</v>
       </c>
       <c r="F71">
-        <v>361.905</v>
+        <v>367.15</v>
       </c>
       <c r="G71">
         <v>6.88</v>
@@ -7234,45 +7234,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M71">
-        <v>27.432399</v>
+        <v>33.0435</v>
       </c>
       <c r="N71">
-        <v>27.70093433333333</v>
+        <v>22.08983333333333</v>
       </c>
       <c r="O71">
-        <v>7.479252269999999</v>
+        <v>5.964255</v>
       </c>
       <c r="P71">
-        <v>20.22168206333333</v>
+        <v>16.12557833333333</v>
       </c>
       <c r="Q71">
-        <v>61.42168206333332</v>
+        <v>57.32557833333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1342203530454364</v>
+        <v>0.1368645240225848</v>
       </c>
       <c r="T71">
-        <v>1.619449817972554</v>
+        <v>1.667878738013518</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.009788984672224</v>
+        <v>1.668507674227407</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08704935720677542</v>
+        <v>0.08715740496946556</v>
       </c>
       <c r="C72">
-        <v>-29.28117875904212</v>
+        <v>-35.39089939702541</v>
       </c>
       <c r="D72">
-        <v>330.9888212409579</v>
+        <v>330.1241006029746</v>
       </c>
       <c r="E72">
-        <v>17.45000000000005</v>
+        <v>22.69500000000005</v>
       </c>
       <c r="F72">
-        <v>367.15</v>
+        <v>372.395</v>
       </c>
       <c r="G72">
         <v>6.88</v>
@@ -7316,28 +7316,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M72">
-        <v>33.0435</v>
+        <v>33.51555</v>
       </c>
       <c r="N72">
-        <v>22.08983333333333</v>
+        <v>21.61778333333333</v>
       </c>
       <c r="O72">
-        <v>5.964255</v>
+        <v>5.836801499999999</v>
       </c>
       <c r="P72">
-        <v>16.12557833333333</v>
+        <v>15.78098183333333</v>
       </c>
       <c r="Q72">
-        <v>57.32557833333333</v>
+        <v>56.98098183333332</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1368645240225848</v>
+        <v>0.1396910516188468</v>
       </c>
       <c r="T72">
-        <v>1.667878738013518</v>
+        <v>1.719647583574549</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.668507674227407</v>
+        <v>1.645007566139697</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08715740496946557</v>
+        <v>0.08726545273215572</v>
       </c>
       <c r="C73">
-        <v>-35.39089939702546</v>
+        <v>-41.49611357847073</v>
       </c>
       <c r="D73">
-        <v>330.1241006029745</v>
+        <v>329.2638864215293</v>
       </c>
       <c r="E73">
-        <v>22.69499999999999</v>
+        <v>27.94</v>
       </c>
       <c r="F73">
-        <v>372.395</v>
+        <v>377.64</v>
       </c>
       <c r="G73">
         <v>6.88</v>
@@ -7398,28 +7398,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M73">
-        <v>33.51555</v>
+        <v>33.9876</v>
       </c>
       <c r="N73">
-        <v>21.61778333333334</v>
+        <v>21.14573333333333</v>
       </c>
       <c r="O73">
-        <v>5.836801500000001</v>
+        <v>5.709348</v>
       </c>
       <c r="P73">
-        <v>15.78098183333334</v>
+        <v>15.43638533333333</v>
       </c>
       <c r="Q73">
-        <v>56.98098183333333</v>
+        <v>56.63638533333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1396910516188468</v>
+        <v>0.1427194740434133</v>
       </c>
       <c r="T73">
-        <v>1.719647583574548</v>
+        <v>1.775114203818509</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.645007566139697</v>
+        <v>1.622160238832202</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08726545273215572</v>
+        <v>0.08737350049484585</v>
       </c>
       <c r="C74">
-        <v>-41.49611357847073</v>
+        <v>-47.59685643964536</v>
       </c>
       <c r="D74">
-        <v>329.2638864215293</v>
+        <v>328.4081435603546</v>
       </c>
       <c r="E74">
-        <v>27.94</v>
+        <v>33.185</v>
       </c>
       <c r="F74">
-        <v>377.64</v>
+        <v>382.885</v>
       </c>
       <c r="G74">
         <v>6.88</v>
@@ -7480,28 +7480,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M74">
-        <v>33.9876</v>
+        <v>34.45965</v>
       </c>
       <c r="N74">
-        <v>21.14573333333333</v>
+        <v>20.67368333333334</v>
       </c>
       <c r="O74">
-        <v>5.709348</v>
+        <v>5.581894500000002</v>
       </c>
       <c r="P74">
-        <v>15.43638533333333</v>
+        <v>15.09178883333334</v>
       </c>
       <c r="Q74">
-        <v>56.63638533333333</v>
+        <v>56.29178883333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1427194740434133</v>
+        <v>0.1459722240549846</v>
       </c>
       <c r="T74">
-        <v>1.775114203818509</v>
+        <v>1.834689462599059</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.622160238832202</v>
+        <v>1.599938865697514</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08737350049484585</v>
+        <v>0.087481548257536</v>
       </c>
       <c r="C75">
-        <v>-47.59685643964536</v>
+        <v>-53.69316275249344</v>
       </c>
       <c r="D75">
-        <v>328.4081435603546</v>
+        <v>327.5568372475066</v>
       </c>
       <c r="E75">
-        <v>33.185</v>
+        <v>38.43000000000001</v>
       </c>
       <c r="F75">
-        <v>382.885</v>
+        <v>388.13</v>
       </c>
       <c r="G75">
         <v>6.88</v>
@@ -7562,28 +7562,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M75">
-        <v>34.45965</v>
+        <v>34.9317</v>
       </c>
       <c r="N75">
-        <v>20.67368333333334</v>
+        <v>20.20163333333333</v>
       </c>
       <c r="O75">
-        <v>5.581894500000002</v>
+        <v>5.454441</v>
       </c>
       <c r="P75">
-        <v>15.09178883333334</v>
+        <v>14.74719233333333</v>
       </c>
       <c r="Q75">
-        <v>56.29178883333333</v>
+        <v>55.94719233333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1459722240549846</v>
+        <v>0.1494751856059077</v>
       </c>
       <c r="T75">
-        <v>1.834689462599059</v>
+        <v>1.898847433593499</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.599938865697514</v>
+        <v>1.578318070215115</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.087481548257536</v>
+        <v>0.08758959602022615</v>
       </c>
       <c r="C76">
-        <v>-53.69316275249344</v>
+        <v>-59.78506692934462</v>
       </c>
       <c r="D76">
-        <v>327.5568372475066</v>
+        <v>326.7099330706554</v>
       </c>
       <c r="E76">
-        <v>38.43000000000001</v>
+        <v>43.67500000000001</v>
       </c>
       <c r="F76">
-        <v>388.13</v>
+        <v>393.375</v>
       </c>
       <c r="G76">
         <v>6.88</v>
@@ -7644,28 +7644,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M76">
-        <v>34.9317</v>
+        <v>35.40375</v>
       </c>
       <c r="N76">
-        <v>20.20163333333333</v>
+        <v>19.72958333333334</v>
       </c>
       <c r="O76">
-        <v>5.454441</v>
+        <v>5.326987500000001</v>
       </c>
       <c r="P76">
-        <v>14.74719233333333</v>
+        <v>14.40259583333334</v>
       </c>
       <c r="Q76">
-        <v>55.94719233333333</v>
+        <v>55.60259583333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1494751856059077</v>
+        <v>0.1532583840809046</v>
       </c>
       <c r="T76">
-        <v>1.898847433593499</v>
+        <v>1.968138042267493</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.578318070215115</v>
+        <v>1.557273829278914</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08758959602022615</v>
+        <v>0.08769764378291628</v>
       </c>
       <c r="C77">
-        <v>-59.78506692934462</v>
+        <v>-65.87260302755175</v>
       </c>
       <c r="D77">
-        <v>326.7099330706554</v>
+        <v>325.8673969724483</v>
       </c>
       <c r="E77">
-        <v>43.67500000000001</v>
+        <v>48.92000000000002</v>
       </c>
       <c r="F77">
-        <v>393.375</v>
+        <v>398.62</v>
       </c>
       <c r="G77">
         <v>6.88</v>
@@ -7726,28 +7726,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M77">
-        <v>35.40375</v>
+        <v>35.8758</v>
       </c>
       <c r="N77">
-        <v>19.72958333333334</v>
+        <v>19.25753333333333</v>
       </c>
       <c r="O77">
-        <v>5.326987500000001</v>
+        <v>5.199534000000001</v>
       </c>
       <c r="P77">
-        <v>14.40259583333334</v>
+        <v>14.05799933333333</v>
       </c>
       <c r="Q77">
-        <v>55.60259583333333</v>
+        <v>55.25799933333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1532583840809046</v>
+        <v>0.1573568490954845</v>
       </c>
       <c r="T77">
-        <v>1.968138042267493</v>
+        <v>2.043202868330987</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.557273829278914</v>
+        <v>1.536783384156823</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08769764378291628</v>
+        <v>0.08780569154560641</v>
       </c>
       <c r="C78">
-        <v>-65.87260302755175</v>
+        <v>-71.95580475405592</v>
       </c>
       <c r="D78">
-        <v>325.8673969724483</v>
+        <v>325.0291952459441</v>
       </c>
       <c r="E78">
-        <v>48.92000000000002</v>
+        <v>54.16500000000002</v>
       </c>
       <c r="F78">
-        <v>398.62</v>
+        <v>403.865</v>
       </c>
       <c r="G78">
         <v>6.88</v>
@@ -7808,28 +7808,28 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M78">
-        <v>35.8758</v>
+        <v>36.34785</v>
       </c>
       <c r="N78">
-        <v>19.25753333333333</v>
+        <v>18.78548333333333</v>
       </c>
       <c r="O78">
-        <v>5.199534000000001</v>
+        <v>5.0720805</v>
       </c>
       <c r="P78">
-        <v>14.05799933333333</v>
+        <v>13.71340283333333</v>
       </c>
       <c r="Q78">
-        <v>55.25799933333333</v>
+        <v>54.91340283333333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1573568490954845</v>
+        <v>0.1618117023722019</v>
       </c>
       <c r="T78">
-        <v>2.043202868330987</v>
+        <v>2.124795070573914</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.536783384156823</v>
+        <v>1.516825158388552</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08780569154560641</v>
+        <v>0.123372073024954</v>
       </c>
       <c r="C79">
-        <v>-71.95580475405592</v>
+        <v>-226.2249560916624</v>
       </c>
       <c r="D79">
-        <v>325.0291952459441</v>
+        <v>176.0050439083376</v>
       </c>
       <c r="E79">
-        <v>54.16500000000002</v>
+        <v>59.41000000000003</v>
       </c>
       <c r="F79">
-        <v>403.865</v>
+        <v>409.11</v>
       </c>
       <c r="G79">
         <v>6.88</v>
@@ -7890,45 +7890,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M79">
-        <v>36.34785</v>
+        <v>60.057348</v>
       </c>
       <c r="N79">
-        <v>18.78548333333333</v>
+        <v>-4.924014666666672</v>
       </c>
       <c r="O79">
-        <v>5.0720805</v>
+        <v>-1.329483960000001</v>
       </c>
       <c r="P79">
-        <v>13.71340283333333</v>
+        <v>-3.59453070666667</v>
       </c>
       <c r="Q79">
-        <v>54.91340283333333</v>
+        <v>37.60546929333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1618117023722019</v>
+        <v>0.1693154025616465</v>
       </c>
       <c r="T79">
-        <v>2.124795070573914</v>
+        <v>2.262227974734254</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.27</v>
+        <v>0.2478630924562303</v>
       </c>
       <c r="W79">
-        <v>0.06569999999999999</v>
+        <v>0.1104136980274254</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.516825158388552</v>
+        <v>0.9180114535415937</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.123372073024954</v>
+        <v>0.124382073024954</v>
       </c>
       <c r="C80">
-        <v>-226.2249560916624</v>
+        <v>-233.7321144632158</v>
       </c>
       <c r="D80">
-        <v>176.0050439083376</v>
+        <v>173.7428855367842</v>
       </c>
       <c r="E80">
-        <v>59.41000000000003</v>
+        <v>64.65500000000003</v>
       </c>
       <c r="F80">
-        <v>409.11</v>
+        <v>414.355</v>
       </c>
       <c r="G80">
         <v>6.88</v>
@@ -7972,37 +7972,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M80">
-        <v>60.057348</v>
+        <v>60.82731400000001</v>
       </c>
       <c r="N80">
-        <v>-4.924014666666672</v>
+        <v>-5.693980666666675</v>
       </c>
       <c r="O80">
-        <v>-1.329483960000001</v>
+        <v>-1.537374780000002</v>
       </c>
       <c r="P80">
-        <v>-3.59453070666667</v>
+        <v>-4.156605886666673</v>
       </c>
       <c r="Q80">
-        <v>37.60546929333333</v>
+        <v>37.04339411333332</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1693154025616465</v>
+        <v>0.1751970883979155</v>
       </c>
       <c r="T80">
-        <v>2.262227974734254</v>
+        <v>2.369953116388266</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2478630924562303</v>
+        <v>0.2447255849567844</v>
       </c>
       <c r="W80">
-        <v>0.1104136980274254</v>
+        <v>0.1108742841283441</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9180114535415937</v>
+        <v>0.9063910553954976</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.124382073024954</v>
+        <v>0.1253920730249541</v>
       </c>
       <c r="C81">
-        <v>-233.7321144632158</v>
+        <v>-241.1818605858245</v>
       </c>
       <c r="D81">
-        <v>173.7428855367842</v>
+        <v>171.5381394141755</v>
       </c>
       <c r="E81">
-        <v>64.65500000000003</v>
+        <v>69.90000000000003</v>
       </c>
       <c r="F81">
-        <v>414.355</v>
+        <v>419.6</v>
       </c>
       <c r="G81">
         <v>6.88</v>
@@ -8054,37 +8054,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M81">
-        <v>60.82731400000001</v>
+        <v>61.59728000000001</v>
       </c>
       <c r="N81">
-        <v>-5.693980666666675</v>
+        <v>-6.463946666666679</v>
       </c>
       <c r="O81">
-        <v>-1.537374780000002</v>
+        <v>-1.745265600000004</v>
       </c>
       <c r="P81">
-        <v>-4.156605886666673</v>
+        <v>-4.718681066666676</v>
       </c>
       <c r="Q81">
-        <v>37.04339411333332</v>
+        <v>36.48131893333332</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1751970883979155</v>
+        <v>0.1816669428178112</v>
       </c>
       <c r="T81">
-        <v>2.369953116388266</v>
+        <v>2.488450772207679</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2447255849567844</v>
+        <v>0.2416665151448245</v>
       </c>
       <c r="W81">
-        <v>0.1108742841283441</v>
+        <v>0.1113233555767398</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9063910553954976</v>
+        <v>0.8950611672030538</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1253920730249541</v>
+        <v>0.126402073024954</v>
       </c>
       <c r="C82">
-        <v>-241.1818605858245</v>
+        <v>-248.5763527056448</v>
       </c>
       <c r="D82">
-        <v>171.5381394141755</v>
+        <v>169.3886472943553</v>
       </c>
       <c r="E82">
-        <v>69.90000000000003</v>
+        <v>75.14500000000004</v>
       </c>
       <c r="F82">
-        <v>419.6</v>
+        <v>424.845</v>
       </c>
       <c r="G82">
         <v>6.88</v>
@@ -8136,37 +8136,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M82">
-        <v>61.59728000000001</v>
+        <v>62.36724600000001</v>
       </c>
       <c r="N82">
-        <v>-6.463946666666679</v>
+        <v>-7.233912666666676</v>
       </c>
       <c r="O82">
-        <v>-1.745265600000004</v>
+        <v>-1.953156420000003</v>
       </c>
       <c r="P82">
-        <v>-4.718681066666676</v>
+        <v>-5.280756246666673</v>
       </c>
       <c r="Q82">
-        <v>36.48131893333332</v>
+        <v>35.91924375333332</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1816669428178112</v>
+        <v>0.1888178345450645</v>
       </c>
       <c r="T82">
-        <v>2.488450772207679</v>
+        <v>2.619421865481768</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2416665151448245</v>
+        <v>0.2386829779208144</v>
       </c>
       <c r="W82">
-        <v>0.1113233555767398</v>
+        <v>0.1117613388412245</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8950611672030538</v>
+        <v>0.8840110293363495</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.126402073024954</v>
+        <v>0.1274120730249541</v>
       </c>
       <c r="C83">
-        <v>-248.5763527056448</v>
+        <v>-255.9176422302963</v>
       </c>
       <c r="D83">
-        <v>169.3886472943553</v>
+        <v>167.2923577697038</v>
       </c>
       <c r="E83">
-        <v>75.14500000000004</v>
+        <v>80.39000000000004</v>
       </c>
       <c r="F83">
-        <v>424.845</v>
+        <v>430.09</v>
       </c>
       <c r="G83">
         <v>6.88</v>
@@ -8218,37 +8218,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M83">
-        <v>62.36724600000001</v>
+        <v>63.13721200000001</v>
       </c>
       <c r="N83">
-        <v>-7.233912666666676</v>
+        <v>-8.003878666666679</v>
       </c>
       <c r="O83">
-        <v>-1.953156420000003</v>
+        <v>-2.161047240000004</v>
       </c>
       <c r="P83">
-        <v>-5.280756246666673</v>
+        <v>-5.842831426666676</v>
       </c>
       <c r="Q83">
-        <v>35.91924375333332</v>
+        <v>35.35716857333332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1888178345450645</v>
+        <v>0.196763269797568</v>
       </c>
       <c r="T83">
-        <v>2.619421865481768</v>
+        <v>2.764945302452977</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2386829779208144</v>
+        <v>0.2357722098973898</v>
       </c>
       <c r="W83">
-        <v>0.1117613388412245</v>
+        <v>0.1121886395870632</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8840110293363495</v>
+        <v>0.8732304070273695</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1274120730249541</v>
+        <v>0.1284220730249541</v>
       </c>
       <c r="C84">
-        <v>-255.9176422302963</v>
+        <v>-263.2076802590125</v>
       </c>
       <c r="D84">
-        <v>167.2923577697038</v>
+        <v>165.2473197409876</v>
       </c>
       <c r="E84">
-        <v>80.39000000000004</v>
+        <v>85.63500000000005</v>
       </c>
       <c r="F84">
-        <v>430.09</v>
+        <v>435.335</v>
       </c>
       <c r="G84">
         <v>6.88</v>
@@ -8300,37 +8300,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M84">
-        <v>63.13721200000001</v>
+        <v>63.90717800000001</v>
       </c>
       <c r="N84">
-        <v>-8.003878666666679</v>
+        <v>-8.773844666666676</v>
       </c>
       <c r="O84">
-        <v>-2.161047240000004</v>
+        <v>-2.368938060000003</v>
       </c>
       <c r="P84">
-        <v>-5.842831426666676</v>
+        <v>-6.404906606666673</v>
       </c>
       <c r="Q84">
-        <v>35.35716857333332</v>
+        <v>34.79509339333332</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.196763269797568</v>
+        <v>0.2056434621386014</v>
       </c>
       <c r="T84">
-        <v>2.764945302452977</v>
+        <v>2.92758914377374</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2357722098973898</v>
+        <v>0.2329315808624815</v>
       </c>
       <c r="W84">
-        <v>0.1121886395870632</v>
+        <v>0.1126056439293877</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8732304070273695</v>
+        <v>0.8627095587499314</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1284220730249541</v>
+        <v>0.1294320730249541</v>
       </c>
       <c r="C85">
-        <v>-263.2076802590125</v>
+        <v>-270.448323639616</v>
       </c>
       <c r="D85">
-        <v>165.2473197409876</v>
+        <v>163.2516763603841</v>
       </c>
       <c r="E85">
-        <v>85.63500000000005</v>
+        <v>90.88000000000005</v>
       </c>
       <c r="F85">
-        <v>435.335</v>
+        <v>440.58</v>
       </c>
       <c r="G85">
         <v>6.88</v>
@@ -8382,37 +8382,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M85">
-        <v>63.90717800000001</v>
+        <v>64.67714400000001</v>
       </c>
       <c r="N85">
-        <v>-8.773844666666676</v>
+        <v>-9.54381066666668</v>
       </c>
       <c r="O85">
-        <v>-2.368938060000003</v>
+        <v>-2.576828880000004</v>
       </c>
       <c r="P85">
-        <v>-6.404906606666673</v>
+        <v>-6.966981786666675</v>
       </c>
       <c r="Q85">
-        <v>34.79509339333332</v>
+        <v>34.23301821333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2056434621386014</v>
+        <v>0.2156336785222641</v>
       </c>
       <c r="T85">
-        <v>2.92758914377374</v>
+        <v>3.1105634652596</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2329315808624815</v>
+        <v>0.2301585858522139</v>
       </c>
       <c r="W85">
-        <v>0.1126056439293877</v>
+        <v>0.113012719596895</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8627095587499314</v>
+        <v>0.8524392068600513</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.129432073024954</v>
+        <v>0.1304420730249541</v>
       </c>
       <c r="C86">
-        <v>-270.4483236396158</v>
+        <v>-277.6413405918398</v>
       </c>
       <c r="D86">
-        <v>163.2516763603842</v>
+        <v>161.3036594081601</v>
       </c>
       <c r="E86">
-        <v>90.88</v>
+        <v>96.125</v>
       </c>
       <c r="F86">
-        <v>440.58</v>
+        <v>445.825</v>
       </c>
       <c r="G86">
         <v>6.88</v>
@@ -8464,37 +8464,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M86">
-        <v>64.677144</v>
+        <v>65.44711000000001</v>
       </c>
       <c r="N86">
-        <v>-9.543810666666666</v>
+        <v>-10.31377666666668</v>
       </c>
       <c r="O86">
-        <v>-2.57682888</v>
+        <v>-2.784719700000003</v>
       </c>
       <c r="P86">
-        <v>-6.966981786666666</v>
+        <v>-7.529056966666674</v>
       </c>
       <c r="Q86">
-        <v>34.23301821333333</v>
+        <v>33.67094303333332</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2156336785222639</v>
+        <v>0.2269559237570815</v>
       </c>
       <c r="T86">
-        <v>3.110563465259597</v>
+        <v>3.317934362943571</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2301585858522139</v>
+        <v>0.2274508377833643</v>
       </c>
       <c r="W86">
-        <v>0.113012719596895</v>
+        <v>0.1134102170134021</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8524392068600515</v>
+        <v>0.8424105103087566</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1304420730249541</v>
+        <v>0.131452073024954</v>
       </c>
       <c r="C87">
-        <v>-277.6413405918398</v>
+        <v>-284.7884159327925</v>
       </c>
       <c r="D87">
-        <v>161.3036594081601</v>
+        <v>159.4015840672075</v>
       </c>
       <c r="E87">
-        <v>96.125</v>
+        <v>101.37</v>
       </c>
       <c r="F87">
-        <v>445.825</v>
+        <v>451.07</v>
       </c>
       <c r="G87">
         <v>6.88</v>
@@ -8546,37 +8546,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M87">
-        <v>65.44711000000001</v>
+        <v>66.21707600000001</v>
       </c>
       <c r="N87">
-        <v>-10.31377666666668</v>
+        <v>-11.08374266666667</v>
       </c>
       <c r="O87">
-        <v>-2.784719700000003</v>
+        <v>-2.992610520000002</v>
       </c>
       <c r="P87">
-        <v>-7.529056966666674</v>
+        <v>-8.091132146666672</v>
       </c>
       <c r="Q87">
-        <v>33.67094303333332</v>
+        <v>33.10886785333332</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2269559237570815</v>
+        <v>0.2398956325968731</v>
       </c>
       <c r="T87">
-        <v>3.317934362943571</v>
+        <v>3.554929674582398</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2274508377833643</v>
+        <v>0.2248060605998368</v>
       </c>
       <c r="W87">
-        <v>0.1134102170134021</v>
+        <v>0.113798470303944</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8424105103087566</v>
+        <v>0.8326150392586548</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.131452073024954</v>
+        <v>0.1324620730249541</v>
       </c>
       <c r="C88">
-        <v>-284.7884159327925</v>
+        <v>-291.8911559370216</v>
       </c>
       <c r="D88">
-        <v>159.4015840672075</v>
+        <v>157.5438440629784</v>
       </c>
       <c r="E88">
-        <v>101.37</v>
+        <v>106.615</v>
       </c>
       <c r="F88">
-        <v>451.07</v>
+        <v>456.315</v>
       </c>
       <c r="G88">
         <v>6.88</v>
@@ -8628,37 +8628,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M88">
-        <v>66.21707600000001</v>
+        <v>66.987042</v>
       </c>
       <c r="N88">
-        <v>-11.08374266666667</v>
+        <v>-11.85370866666667</v>
       </c>
       <c r="O88">
-        <v>-2.992610520000002</v>
+        <v>-3.200501340000001</v>
       </c>
       <c r="P88">
-        <v>-8.091132146666672</v>
+        <v>-8.653207326666669</v>
       </c>
       <c r="Q88">
-        <v>33.10886785333332</v>
+        <v>32.54679267333333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2398956325968731</v>
+        <v>0.2548260658735557</v>
       </c>
       <c r="T88">
-        <v>3.554929674582398</v>
+        <v>3.828385803396428</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2248060605998368</v>
+        <v>0.2222220828917927</v>
       </c>
       <c r="W88">
-        <v>0.113798470303944</v>
+        <v>0.1141777982314848</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8326150392586548</v>
+        <v>0.8230447514510841</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1324620730249541</v>
+        <v>0.1334720730249541</v>
       </c>
       <c r="C89">
-        <v>-291.8911559370216</v>
+        <v>-298.9510928606452</v>
       </c>
       <c r="D89">
-        <v>157.5438440629784</v>
+        <v>155.7289071393548</v>
       </c>
       <c r="E89">
-        <v>106.615</v>
+        <v>111.86</v>
       </c>
       <c r="F89">
-        <v>456.315</v>
+        <v>461.56</v>
       </c>
       <c r="G89">
         <v>6.88</v>
@@ -8710,37 +8710,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M89">
-        <v>66.987042</v>
+        <v>67.75700800000001</v>
       </c>
       <c r="N89">
-        <v>-11.85370866666667</v>
+        <v>-12.62367466666668</v>
       </c>
       <c r="O89">
-        <v>-3.200501340000001</v>
+        <v>-3.408392160000004</v>
       </c>
       <c r="P89">
-        <v>-8.653207326666669</v>
+        <v>-9.215282506666677</v>
       </c>
       <c r="Q89">
-        <v>32.54679267333333</v>
+        <v>31.98471749333332</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2548260658735557</v>
+        <v>0.272244904696352</v>
       </c>
       <c r="T89">
-        <v>3.828385803396428</v>
+        <v>4.147417953679465</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2222220828917927</v>
+        <v>0.2196968319498405</v>
       </c>
       <c r="W89">
-        <v>0.1141777982314848</v>
+        <v>0.1145485050697634</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8230447514510841</v>
+        <v>0.8136919701845944</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1334720730249541</v>
+        <v>0.134482073024954</v>
       </c>
       <c r="C90">
-        <v>-298.9510928606452</v>
+        <v>-305.9696891563304</v>
       </c>
       <c r="D90">
-        <v>155.7289071393548</v>
+        <v>153.9553108436696</v>
       </c>
       <c r="E90">
-        <v>111.86</v>
+        <v>117.105</v>
       </c>
       <c r="F90">
-        <v>461.56</v>
+        <v>466.805</v>
       </c>
       <c r="G90">
         <v>6.88</v>
@@ -8792,37 +8792,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M90">
-        <v>67.75700800000001</v>
+        <v>68.52697400000001</v>
       </c>
       <c r="N90">
-        <v>-12.62367466666668</v>
+        <v>-13.39364066666668</v>
       </c>
       <c r="O90">
-        <v>-3.408392160000004</v>
+        <v>-3.616282980000003</v>
       </c>
       <c r="P90">
-        <v>-9.215282506666677</v>
+        <v>-9.777357686666674</v>
       </c>
       <c r="Q90">
-        <v>31.98471749333332</v>
+        <v>31.42264231333332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.272244904696352</v>
+        <v>0.2928308051232931</v>
       </c>
       <c r="T90">
-        <v>4.147417953679465</v>
+        <v>4.524455949468507</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2196968319498405</v>
+        <v>0.217228328220067</v>
       </c>
       <c r="W90">
-        <v>0.1145485050697634</v>
+        <v>0.1149108814172942</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8136919701845944</v>
+        <v>0.8045493637780259</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.134482073024954</v>
+        <v>0.1858434762309539</v>
       </c>
       <c r="C91">
-        <v>-305.9696891563304</v>
+        <v>-367.6783032336207</v>
       </c>
       <c r="D91">
-        <v>153.9553108436696</v>
+        <v>97.49169676637933</v>
       </c>
       <c r="E91">
-        <v>117.105</v>
+        <v>122.35</v>
       </c>
       <c r="F91">
-        <v>466.805</v>
+        <v>472.05</v>
       </c>
       <c r="G91">
         <v>6.88</v>
@@ -8874,45 +8874,45 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M91">
-        <v>68.52697400000001</v>
+        <v>94.78764000000001</v>
       </c>
       <c r="N91">
-        <v>-13.39364066666668</v>
+        <v>-39.65430666666668</v>
       </c>
       <c r="O91">
-        <v>-3.616282980000003</v>
+        <v>-10.7066628</v>
       </c>
       <c r="P91">
-        <v>-9.777357686666674</v>
+        <v>-28.94764386666667</v>
       </c>
       <c r="Q91">
-        <v>31.42264231333332</v>
+        <v>12.25235613333332</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2928308051232931</v>
+        <v>0.3350479176956209</v>
       </c>
       <c r="T91">
-        <v>4.524455949468507</v>
+        <v>5.297677192268236</v>
       </c>
       <c r="U91">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.217228328220067</v>
+        <v>0.1570457920463048</v>
       </c>
       <c r="W91">
-        <v>0.1149108814172942</v>
+        <v>0.169265204957102</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8045493637780259</v>
+        <v>0.5816510816529805</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1858434762309539</v>
+        <v>0.1873934762309539</v>
       </c>
       <c r="C92">
-        <v>-367.6783032336207</v>
+        <v>-373.9905284618608</v>
       </c>
       <c r="D92">
-        <v>97.49169676637933</v>
+        <v>96.42447153813923</v>
       </c>
       <c r="E92">
-        <v>122.35</v>
+        <v>127.595</v>
       </c>
       <c r="F92">
-        <v>472.05</v>
+        <v>477.295</v>
       </c>
       <c r="G92">
         <v>6.88</v>
@@ -8956,37 +8956,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M92">
-        <v>94.78764000000001</v>
+        <v>95.84083600000001</v>
       </c>
       <c r="N92">
-        <v>-39.65430666666668</v>
+        <v>-40.70750266666668</v>
       </c>
       <c r="O92">
-        <v>-10.7066628</v>
+        <v>-10.99102572</v>
       </c>
       <c r="P92">
-        <v>-28.94764386666667</v>
+        <v>-29.71647694666667</v>
       </c>
       <c r="Q92">
-        <v>12.25235613333332</v>
+        <v>11.48352305333332</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3350479176956209</v>
+        <v>0.3671865752173566</v>
       </c>
       <c r="T92">
-        <v>5.297677192268236</v>
+        <v>5.886307991409152</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1570457920463048</v>
+        <v>0.15532001411173</v>
       </c>
       <c r="W92">
-        <v>0.169265204957102</v>
+        <v>0.1696117411663646</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5816510816529805</v>
+        <v>0.5752593115249258</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1873934762309539</v>
+        <v>0.1889434762309539</v>
       </c>
       <c r="C93">
-        <v>-373.9905284618608</v>
+        <v>-380.2796412277334</v>
       </c>
       <c r="D93">
-        <v>96.42447153813923</v>
+        <v>95.38035877226667</v>
       </c>
       <c r="E93">
-        <v>127.595</v>
+        <v>132.84</v>
       </c>
       <c r="F93">
-        <v>477.295</v>
+        <v>482.54</v>
       </c>
       <c r="G93">
         <v>6.88</v>
@@ -9038,37 +9038,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M93">
-        <v>95.84083600000001</v>
+        <v>96.89403200000001</v>
       </c>
       <c r="N93">
-        <v>-40.70750266666668</v>
+        <v>-41.76069866666668</v>
       </c>
       <c r="O93">
-        <v>-10.99102572</v>
+        <v>-11.27538864</v>
       </c>
       <c r="P93">
-        <v>-29.71647694666667</v>
+        <v>-30.48531002666667</v>
       </c>
       <c r="Q93">
-        <v>11.48352305333332</v>
+        <v>10.71468997333332</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3671865752173566</v>
+        <v>0.4073598971195262</v>
       </c>
       <c r="T93">
-        <v>5.886307991409152</v>
+        <v>6.622096490335298</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.15532001411173</v>
+        <v>0.1536317530887764</v>
       </c>
       <c r="W93">
-        <v>0.1696117411663646</v>
+        <v>0.1699507439797737</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5752593115249258</v>
+        <v>0.569006492921394</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1889434762309539</v>
+        <v>0.1904934762309539</v>
       </c>
       <c r="C94">
-        <v>-380.2796412277334</v>
+        <v>-386.546384294166</v>
       </c>
       <c r="D94">
-        <v>95.38035877226667</v>
+        <v>94.35861570583397</v>
       </c>
       <c r="E94">
-        <v>132.84</v>
+        <v>138.085</v>
       </c>
       <c r="F94">
-        <v>482.54</v>
+        <v>487.785</v>
       </c>
       <c r="G94">
         <v>6.88</v>
@@ -9120,37 +9120,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M94">
-        <v>96.89403200000001</v>
+        <v>97.94722800000001</v>
       </c>
       <c r="N94">
-        <v>-41.76069866666668</v>
+        <v>-42.81389466666668</v>
       </c>
       <c r="O94">
-        <v>-11.27538864</v>
+        <v>-11.55975156</v>
       </c>
       <c r="P94">
-        <v>-30.48531002666667</v>
+        <v>-31.25414310666667</v>
       </c>
       <c r="Q94">
-        <v>10.71468997333332</v>
+        <v>9.945856893333321</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4073598971195262</v>
+        <v>0.4590113109937444</v>
       </c>
       <c r="T94">
-        <v>6.622096490335298</v>
+        <v>7.568110274668913</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1536317530887764</v>
+        <v>0.1519797987544885</v>
       </c>
       <c r="W94">
-        <v>0.1699507439797737</v>
+        <v>0.1702824564100987</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.569006492921394</v>
+        <v>0.5628881435351425</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1904934762309539</v>
+        <v>0.1920434762309539</v>
       </c>
       <c r="C95">
-        <v>-386.546384294166</v>
+        <v>-392.7914689346122</v>
       </c>
       <c r="D95">
-        <v>94.35861570583397</v>
+        <v>93.35853106538779</v>
       </c>
       <c r="E95">
-        <v>138.085</v>
+        <v>143.33</v>
       </c>
       <c r="F95">
-        <v>487.785</v>
+        <v>493.03</v>
       </c>
       <c r="G95">
         <v>6.88</v>
@@ -9202,37 +9202,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M95">
-        <v>97.94722800000001</v>
+        <v>99.00042400000001</v>
       </c>
       <c r="N95">
-        <v>-42.81389466666668</v>
+        <v>-43.86709066666668</v>
       </c>
       <c r="O95">
-        <v>-11.55975156</v>
+        <v>-11.84411448</v>
       </c>
       <c r="P95">
-        <v>-31.25414310666667</v>
+        <v>-32.02297618666667</v>
       </c>
       <c r="Q95">
-        <v>9.945856893333321</v>
+        <v>9.177023813333321</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4590113109937444</v>
+        <v>0.5278798628260352</v>
       </c>
       <c r="T95">
-        <v>7.568110274668913</v>
+        <v>8.829461987113733</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1519797987544885</v>
+        <v>0.1503629923847599</v>
       </c>
       <c r="W95">
-        <v>0.1702824564100987</v>
+        <v>0.1706071111291402</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5628881435351425</v>
+        <v>0.556899971795407</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1920434762309539</v>
+        <v>0.1935934762309539</v>
       </c>
       <c r="C96">
-        <v>-392.7914689346122</v>
+        <v>-399.0155765842979</v>
       </c>
       <c r="D96">
-        <v>93.35853106538779</v>
+        <v>92.37942341570216</v>
       </c>
       <c r="E96">
-        <v>143.33</v>
+        <v>148.575</v>
       </c>
       <c r="F96">
-        <v>493.03</v>
+        <v>498.275</v>
       </c>
       <c r="G96">
         <v>6.88</v>
@@ -9284,37 +9284,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M96">
-        <v>99.00042400000001</v>
+        <v>100.05362</v>
       </c>
       <c r="N96">
-        <v>-43.86709066666668</v>
+        <v>-44.92028666666668</v>
       </c>
       <c r="O96">
-        <v>-11.84411448</v>
+        <v>-12.1284774</v>
       </c>
       <c r="P96">
-        <v>-32.02297618666667</v>
+        <v>-32.79180926666668</v>
       </c>
       <c r="Q96">
-        <v>9.177023813333321</v>
+        <v>8.408190733333321</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5278798628260352</v>
+        <v>0.6242958353912424</v>
       </c>
       <c r="T96">
-        <v>8.829461987113733</v>
+        <v>10.59535438453648</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1503629923847599</v>
+        <v>0.1487802240438677</v>
       </c>
       <c r="W96">
-        <v>0.1706071111291402</v>
+        <v>0.1709249310119914</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.556899971795407</v>
+        <v>0.5510378668291395</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1935934762309539</v>
+        <v>0.1951434762309539</v>
       </c>
       <c r="C97">
-        <v>-399.0155765842979</v>
+        <v>-405.2193603886396</v>
       </c>
       <c r="D97">
-        <v>92.37942341570216</v>
+        <v>91.42063961136043</v>
       </c>
       <c r="E97">
-        <v>148.575</v>
+        <v>153.8200000000001</v>
       </c>
       <c r="F97">
-        <v>498.275</v>
+        <v>503.52</v>
       </c>
       <c r="G97">
         <v>6.88</v>
@@ -9366,37 +9366,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M97">
-        <v>100.05362</v>
+        <v>101.106816</v>
       </c>
       <c r="N97">
-        <v>-44.92028666666668</v>
+        <v>-45.97348266666668</v>
       </c>
       <c r="O97">
-        <v>-12.1284774</v>
+        <v>-12.41284032</v>
       </c>
       <c r="P97">
-        <v>-32.79180926666668</v>
+        <v>-33.56064234666668</v>
       </c>
       <c r="Q97">
-        <v>8.408190733333321</v>
+        <v>7.63935765333332</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6242958353912424</v>
+        <v>0.7689197942390533</v>
       </c>
       <c r="T97">
-        <v>10.59535438453648</v>
+        <v>13.24419298067061</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1487802240438677</v>
+        <v>0.1472304300434107</v>
       </c>
       <c r="W97">
-        <v>0.1709249310119914</v>
+        <v>0.1712361296472831</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5510378668291395</v>
+        <v>0.5452978890496694</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1951434762309539</v>
+        <v>0.1966934762309539</v>
       </c>
       <c r="C98">
-        <v>-405.2193603886395</v>
+        <v>-411.4034466562309</v>
       </c>
       <c r="D98">
-        <v>91.42063961136043</v>
+        <v>90.48155334376906</v>
       </c>
       <c r="E98">
-        <v>153.82</v>
+        <v>159.065</v>
       </c>
       <c r="F98">
-        <v>503.52</v>
+        <v>508.765</v>
       </c>
       <c r="G98">
         <v>6.88</v>
@@ -9448,37 +9448,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M98">
-        <v>101.106816</v>
+        <v>102.160012</v>
       </c>
       <c r="N98">
-        <v>-45.97348266666666</v>
+        <v>-47.02667866666666</v>
       </c>
       <c r="O98">
-        <v>-12.41284032</v>
+        <v>-12.69720324</v>
       </c>
       <c r="P98">
-        <v>-33.56064234666666</v>
+        <v>-34.32947542666666</v>
       </c>
       <c r="Q98">
-        <v>7.639357653333334</v>
+        <v>6.870524573333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7689197942390514</v>
+        <v>1.009959725652069</v>
       </c>
       <c r="T98">
-        <v>13.24419298067058</v>
+        <v>17.65892397422744</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1472304300434107</v>
+        <v>0.1457125905584271</v>
       </c>
       <c r="W98">
-        <v>0.1712361296472831</v>
+        <v>0.1715409118158678</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5452978890496694</v>
+        <v>0.5396762613275079</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1966934762309539</v>
+        <v>0.1982434762309539</v>
       </c>
       <c r="C99">
-        <v>-411.4034466562309</v>
+        <v>-417.568436223186</v>
       </c>
       <c r="D99">
-        <v>90.48155334376906</v>
+        <v>89.56156377681398</v>
       </c>
       <c r="E99">
-        <v>159.065</v>
+        <v>164.31</v>
       </c>
       <c r="F99">
-        <v>508.765</v>
+        <v>514.01</v>
       </c>
       <c r="G99">
         <v>6.88</v>
@@ -9530,37 +9530,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M99">
-        <v>102.160012</v>
+        <v>103.213208</v>
       </c>
       <c r="N99">
-        <v>-47.02667866666666</v>
+        <v>-48.07987466666666</v>
       </c>
       <c r="O99">
-        <v>-12.69720324</v>
+        <v>-12.98156616</v>
       </c>
       <c r="P99">
-        <v>-34.32947542666666</v>
+        <v>-35.09830850666666</v>
       </c>
       <c r="Q99">
-        <v>6.870524573333334</v>
+        <v>6.101691493333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.009959725652069</v>
+        <v>1.492039588478103</v>
       </c>
       <c r="T99">
-        <v>17.65892397422744</v>
+        <v>26.48838596134115</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1457125905584271</v>
+        <v>0.1442257273894636</v>
       </c>
       <c r="W99">
-        <v>0.1715409118158678</v>
+        <v>0.1718394739401957</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5396762613275079</v>
+        <v>0.5341693607017169</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1982434762309539</v>
+        <v>0.1997934762309539</v>
       </c>
       <c r="C100">
-        <v>-417.568436223186</v>
+        <v>-423.7149057350883</v>
       </c>
       <c r="D100">
-        <v>89.56156377681398</v>
+        <v>88.66009426491166</v>
       </c>
       <c r="E100">
-        <v>164.31</v>
+        <v>169.555</v>
       </c>
       <c r="F100">
-        <v>514.01</v>
+        <v>519.255</v>
       </c>
       <c r="G100">
         <v>6.88</v>
@@ -9612,37 +9612,37 @@
         <v>55.13333333333333</v>
       </c>
       <c r="M100">
-        <v>103.213208</v>
+        <v>104.266404</v>
       </c>
       <c r="N100">
-        <v>-48.07987466666666</v>
+        <v>-49.13307066666668</v>
       </c>
       <c r="O100">
-        <v>-12.98156616</v>
+        <v>-13.26592908</v>
       </c>
       <c r="P100">
-        <v>-35.09830850666666</v>
+        <v>-35.86714158666668</v>
       </c>
       <c r="Q100">
-        <v>6.101691493333334</v>
+        <v>5.332858413333319</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.492039588478103</v>
+        <v>2.938279176956206</v>
       </c>
       <c r="T100">
-        <v>26.48838596134115</v>
+        <v>52.97677192268231</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1442257273894636</v>
+        <v>0.142768901860277</v>
       </c>
       <c r="W100">
-        <v>0.1718394739401957</v>
+        <v>0.1721320045064564</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5341693607017169</v>
+        <v>0.5287737105936188</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1997934762309539</v>
-      </c>
-      <c r="C101">
-        <v>-423.7149057350883</v>
-      </c>
-      <c r="D101">
-        <v>88.66009426491166</v>
-      </c>
-      <c r="E101">
-        <v>169.555</v>
-      </c>
-      <c r="F101">
-        <v>519.255</v>
-      </c>
-      <c r="G101">
-        <v>6.88</v>
-      </c>
-      <c r="H101">
-        <v>174.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>96.33333333333333</v>
-      </c>
-      <c r="K101">
-        <v>41.2</v>
-      </c>
-      <c r="L101">
-        <v>55.13333333333333</v>
-      </c>
-      <c r="M101">
-        <v>104.266404</v>
-      </c>
-      <c r="N101">
-        <v>-49.13307066666668</v>
-      </c>
-      <c r="O101">
-        <v>-13.26592908</v>
-      </c>
-      <c r="P101">
-        <v>-35.86714158666668</v>
-      </c>
-      <c r="Q101">
-        <v>5.332858413333319</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.938279176956206</v>
-      </c>
-      <c r="T101">
-        <v>52.97677192268231</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.142768901860277</v>
-      </c>
-      <c r="W101">
-        <v>0.1721320045064564</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5287737105936188</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
